--- a/AAII_Financials/Quarterly/VYNE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VYNE_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
   <si>
     <t>VYNE</t>
   </si>
@@ -656,107 +656,110 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -770,44 +773,44 @@
         <v>100</v>
       </c>
       <c r="G8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
         <v>200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1800</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
       <c r="T8" s="3">
         <v>0</v>
       </c>
@@ -815,13 +818,16 @@
         <v>0</v>
       </c>
       <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
         <v>300</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -846,33 +852,33 @@
       <c r="J9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L9" s="3">
         <v>900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>300</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>5</v>
       </c>
@@ -885,8 +891,11 @@
       <c r="W9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -911,33 +920,33 @@
       <c r="J10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K10" s="3">
-        <v>0</v>
+      <c r="K10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
         <v>3100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>11500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1500</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>5</v>
       </c>
@@ -950,8 +959,11 @@
       <c r="W10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -975,73 +987,77 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E12" s="3">
         <v>3300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>4300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>19500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>7800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>6600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>13100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>16000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>11800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>12500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>12600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>10800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1105,8 +1121,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1170,8 +1189,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1235,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E17" s="3">
         <v>6300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>39800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>21900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>26300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>26800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>178900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>41600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>21900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>23200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>19400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>16200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-6200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-10400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-9300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-38900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-17800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-9800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-22000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-23500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-167200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-39800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-21900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-23200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-19400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-15900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-18400</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,58 +1444,59 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>700</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
-      </c>
-      <c r="E20" s="3">
-        <v>300</v>
       </c>
       <c r="F20" s="3">
         <v>300</v>
       </c>
       <c r="G20" s="3">
+        <v>300</v>
+      </c>
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>700</v>
-      </c>
-      <c r="S20" s="3">
-        <v>400</v>
       </c>
       <c r="T20" s="3">
         <v>400</v>
@@ -1472,92 +1505,98 @@
         <v>400</v>
       </c>
       <c r="V20" s="3">
+        <v>400</v>
+      </c>
+      <c r="W20" s="3">
         <v>500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-10000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-5600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-7900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-9100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-8200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-8700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-38900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-17800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-9600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-9800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-21900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-23600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-166500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-39100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-21700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-22700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-18900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-15300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>5</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -1569,22 +1608,22 @@
         <v>0</v>
       </c>
       <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>5600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3500</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1100</v>
       </c>
       <c r="N22" s="3">
         <v>1100</v>
       </c>
       <c r="O22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P22" s="3">
         <v>1200</v>
-      </c>
-      <c r="P22" s="3">
-        <v>1100</v>
       </c>
       <c r="Q22" s="3">
         <v>1100</v>
@@ -1592,88 +1631,94 @@
       <c r="R22" s="3">
         <v>1100</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T22" s="3">
+      <c r="S22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U22" s="3">
         <v>300</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-10000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-44700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-21300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-10700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-23200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-24700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-167700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-40200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-21500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-23200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-19000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-15400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1699,11 +1744,11 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-400</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
@@ -1717,28 +1762,31 @@
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>-300</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>-200</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-10000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-7800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-8200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-44200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-21300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-10700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-10900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-23200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-24700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-167400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-40200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-21500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-23200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-19000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-15200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-7800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-44200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-21300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-10700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-10900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-23200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-24700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-167400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-40200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-21500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-23200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-19000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-15200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,49 +2054,52 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>-500</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-2200</v>
-      </c>
-      <c r="H29" s="3">
-        <v>-200</v>
       </c>
       <c r="I29" s="3">
         <v>-200</v>
       </c>
       <c r="J29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K29" s="3">
         <v>13400</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-29100</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M29" s="3">
+      <c r="M29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N29" s="3">
         <v>-9200</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-9700</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -2053,8 +2113,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
@@ -2062,8 +2122,11 @@
       <c r="W29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,58 +2258,61 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-300</v>
       </c>
       <c r="F32" s="3">
         <v>-300</v>
       </c>
       <c r="G32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-700</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-400</v>
       </c>
       <c r="T32" s="3">
         <v>-400</v>
@@ -2252,78 +2321,84 @@
         <v>-400</v>
       </c>
       <c r="V32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="W32" s="3">
         <v>-500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-10100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-73300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-21300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-19900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-20600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-23200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-24700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-167400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-40200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-21500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-23200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-19000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-15200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-10100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-73300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-21300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-19900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-20600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-23200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-24700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-167400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-40200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-21500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-23200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-19000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-15200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,73 +2657,77 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E41" s="3">
         <v>15400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>20600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>30200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>30900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>35500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>42800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>50500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>42300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>52300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>103400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>118500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>57600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>73000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>96500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>57600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>43800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>34200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>65100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>62000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>49500</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2688,141 +2777,147 @@
         <v>0</v>
       </c>
       <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
         <v>12100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>57100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>44400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>59600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
         <v>300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>15800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>8300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>100</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3">
+        <v>0</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L44" s="3">
         <v>7300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1400</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2832,138 +2927,147 @@
       <c r="W44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>65300</v>
+      </c>
+      <c r="E45" s="3">
         <v>1800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>29300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>19100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2100</v>
-      </c>
-      <c r="U45" s="3">
-        <v>3700</v>
       </c>
       <c r="V45" s="3">
         <v>3700</v>
       </c>
       <c r="W45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="X45" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E46" s="3">
         <v>17500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>23000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>33000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>38300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>44000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>51900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>60700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>63200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>76100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>128400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>143100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>87300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>98200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>119300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>98400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>76400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>93400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>113100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>125200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>139500</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3012,28 +3116,31 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T47" s="3">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U47" s="3">
         <v>2000</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>5</v>
+      <c r="D48" s="3">
+        <v>200</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>5</v>
@@ -3041,59 +3148,62 @@
       <c r="F48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G48" s="3">
-        <v>0</v>
+      <c r="G48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H48" s="3">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3">
         <v>100</v>
-      </c>
-      <c r="I48" s="3">
-        <v>300</v>
       </c>
       <c r="J48" s="3">
         <v>300</v>
       </c>
       <c r="K48" s="3">
+        <v>300</v>
+      </c>
+      <c r="L48" s="3">
         <v>400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5400</v>
-      </c>
-      <c r="R48" s="3">
-        <v>4600</v>
       </c>
       <c r="S48" s="3">
         <v>4600</v>
       </c>
       <c r="T48" s="3">
+        <v>4600</v>
+      </c>
+      <c r="U48" s="3">
         <v>900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3133,20 +3243,20 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>5</v>
+      <c r="P49" s="3">
+        <v>0</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R49" s="3">
+      <c r="R49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S49" s="3">
         <v>4000</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
-      </c>
-      <c r="T49" s="3" t="s">
-        <v>5</v>
+      <c r="T49" s="3">
+        <v>0</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>5</v>
@@ -3157,8 +3267,11 @@
       <c r="W49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,73 +3403,79 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E52" s="3">
         <v>1800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>53500</v>
-      </c>
-      <c r="S52" s="3">
-        <v>200</v>
       </c>
       <c r="T52" s="3">
         <v>200</v>
       </c>
       <c r="U52" s="3">
+        <v>200</v>
+      </c>
+      <c r="V52" s="3">
         <v>100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,73 +3539,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>97700</v>
+      </c>
+      <c r="E54" s="3">
         <v>19300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>25000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>35300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>40800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>46900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>55200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>64300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>67000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>81300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>134000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>149200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>93700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>107700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>130800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>160500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>81200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>96600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>114400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>126300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>139900</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,73 +3661,77 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E57" s="3">
         <v>700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>14100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>19400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3630,11 +3763,11 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>33400</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>5</v>
       </c>
@@ -3650,8 +3783,8 @@
       <c r="S58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -3662,138 +3795,147 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E59" s="3">
         <v>5700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>18100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>42500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>16900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6400</v>
+        <v>7500</v>
       </c>
       <c r="E60" s="3">
         <v>6400</v>
       </c>
       <c r="F60" s="3">
+        <v>6400</v>
+      </c>
+      <c r="G60" s="3">
         <v>7500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9300</v>
-      </c>
-      <c r="H60" s="3">
-        <v>6800</v>
       </c>
       <c r="I60" s="3">
         <v>6800</v>
       </c>
       <c r="J60" s="3">
+        <v>6800</v>
+      </c>
+      <c r="K60" s="3">
         <v>8600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>21000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>57600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>21500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>21800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>23200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>24200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>56600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>29300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3828,26 +3970,26 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>33300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>33200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>33000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>32900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>32800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>32700</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -3857,13 +3999,16 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="E62" s="3">
         <v>1300</v>
@@ -3871,8 +4016,8 @@
       <c r="F62" s="3">
         <v>1300</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>5</v>
+      <c r="G62" s="3">
+        <v>1300</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>5</v>
@@ -3883,47 +4028,50 @@
       <c r="J62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
         <v>1400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>300</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
-      </c>
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,73 +4271,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E66" s="3">
         <v>7800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9300</v>
-      </c>
-      <c r="H66" s="3">
-        <v>6800</v>
       </c>
       <c r="I66" s="3">
         <v>6800</v>
       </c>
       <c r="J66" s="3">
+        <v>6800</v>
+      </c>
+      <c r="K66" s="3">
         <v>8600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>18400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>22400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>59100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>56300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>56200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>58200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>59300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>91000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>63600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>12200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>10600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4352,11 +4519,11 @@
         <v>0</v>
       </c>
       <c r="G70" s="3">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3">
         <v>200</v>
       </c>
-      <c r="H70" s="3">
-        <v>0</v>
-      </c>
       <c r="I70" s="3">
         <v>0</v>
       </c>
@@ -4402,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,73 +4637,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-691300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-685100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-678600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-668500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-662700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-652800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-643300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-634900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-639500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-628000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-606700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-586700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-566200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-543000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-518300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-350900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-310600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-162800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-146000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-129500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-110600</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,73 +4909,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>88700</v>
+      </c>
+      <c r="E76" s="3">
         <v>11500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>17300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>26400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>31200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>40100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>48400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>55700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>48600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>58900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>74900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>92900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>37500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>49500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>71500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>69500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>87000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>102200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>115600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>130400</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-10100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-73300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-21300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-19900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-20600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-23200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-24700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-167400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-40200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-21500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-23200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-19000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-15200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,8 +5214,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5032,23 +5230,23 @@
         <v>0</v>
       </c>
       <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
         <v>-200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
       <c r="J83" s="3">
         <v>0</v>
       </c>
       <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
@@ -5056,7 +5254,7 @@
         <v>0</v>
       </c>
       <c r="O83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P83" s="3">
         <v>100</v>
@@ -5068,10 +5266,10 @@
         <v>100</v>
       </c>
       <c r="S83" s="3">
+        <v>100</v>
+      </c>
+      <c r="T83" s="3">
         <v>-200</v>
-      </c>
-      <c r="T83" s="3">
-        <v>100</v>
       </c>
       <c r="U83" s="3">
         <v>100</v>
@@ -5080,10 +5278,13 @@
         <v>100</v>
       </c>
       <c r="W83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-9600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-9200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-9000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-56400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-17500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-16300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-12600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-25400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-23600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-35900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-52200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-16400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-19300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-12700</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-16600</v>
       </c>
       <c r="W89" s="3">
         <v>-16600</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3">
+        <v>-16600</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,8 +5716,9 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5521,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
@@ -5530,7 +5750,7 @@
         <v>-100</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -5542,11 +5762,11 @@
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
@@ -5562,8 +5782,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,73 +5918,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-62400</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>5000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>16700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1000</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>1000</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>2000</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>21100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>66000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>5500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-7100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>15400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>27500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5847,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,73 +6284,79 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>82700</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>200</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>39800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-33600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>73500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>8000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>53600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-23000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>23000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3000</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6157,11 +6405,11 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -6169,72 +6417,78 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-9600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>8200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-15600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-51100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-15400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>61000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-15400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-23600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>38900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>13900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-31400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>12400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-20700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VYNE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VYNE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
   <si>
     <t>VYNE</t>
   </si>
@@ -656,110 +656,114 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -776,44 +780,44 @@
         <v>100</v>
       </c>
       <c r="H8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
         <v>200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1800</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
@@ -821,13 +825,16 @@
         <v>0</v>
       </c>
       <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
         <v>300</v>
       </c>
-      <c r="X8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -855,33 +862,33 @@
       <c r="K9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="3">
         <v>900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>300</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>5</v>
       </c>
@@ -894,8 +901,11 @@
       <c r="X9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -923,33 +933,33 @@
       <c r="K10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L10" s="3">
-        <v>0</v>
+      <c r="L10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
         <v>3100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>11500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1500</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>5</v>
       </c>
@@ -962,8 +972,11 @@
       <c r="X10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,76 +1001,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E12" s="3">
         <v>3000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>7200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>19500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>7000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>7800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>6600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>13100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>16000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>11800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>12500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>12600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>10800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,8 +1141,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1192,8 +1212,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1260,8 +1283,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1309,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E17" s="3">
         <v>6900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>39800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>21900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>26300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>26800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>178900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>41600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>21900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>23200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>19400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>16200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-6800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-6200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-9300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-38900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-17800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-9500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-9800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-23500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-167200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-39800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-21900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-23200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-19400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-15900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-18400</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,61 +1478,62 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
-      </c>
-      <c r="F20" s="3">
-        <v>300</v>
       </c>
       <c r="G20" s="3">
         <v>300</v>
       </c>
       <c r="H20" s="3">
+        <v>300</v>
+      </c>
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>700</v>
-      </c>
-      <c r="T20" s="3">
-        <v>400</v>
       </c>
       <c r="U20" s="3">
         <v>400</v>
@@ -1508,13 +1542,16 @@
         <v>400</v>
       </c>
       <c r="W20" s="3">
+        <v>400</v>
+      </c>
+      <c r="X20" s="3">
         <v>500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1522,84 +1559,87 @@
         <v>-6200</v>
       </c>
       <c r="E21" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-6100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-10000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-5600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-7900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-9100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-8200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-38900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-17800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-9600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-9800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-21900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-23600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-166500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-39100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-21700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-22700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-18900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-15300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>5</v>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -1611,22 +1651,22 @@
         <v>0</v>
       </c>
       <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
         <v>5600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>3500</v>
-      </c>
-      <c r="N22" s="3">
-        <v>1100</v>
       </c>
       <c r="O22" s="3">
         <v>1100</v>
       </c>
       <c r="P22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Q22" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>1100</v>
       </c>
       <c r="R22" s="3">
         <v>1100</v>
@@ -1634,23 +1674,26 @@
       <c r="S22" s="3">
         <v>1100</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U22" s="3">
+      <c r="T22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V22" s="3">
         <v>300</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1658,67 +1701,70 @@
         <v>-6200</v>
       </c>
       <c r="E23" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-6100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-44700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-21300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-10900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-23200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-24700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-167700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-40200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-21500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-23200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-19000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-15400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1747,11 +1793,11 @@
         <v>0</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-400</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
@@ -1765,28 +1811,31 @@
         <v>0</v>
       </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>-300</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>-200</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,8 +1902,11 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1862,67 +1914,70 @@
         <v>-6200</v>
       </c>
       <c r="E26" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-6100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-8700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-44200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-21300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-10700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-10900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-23200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-24700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-167400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-40200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-21500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-23200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-19000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-15200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1930,67 +1985,70 @@
         <v>-6200</v>
       </c>
       <c r="E27" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-6100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-44200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-21300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-10700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-10900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-23200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-24700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-167400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-40200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-21500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-23200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-19000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-15200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2066,43 +2127,43 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>-500</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-2200</v>
-      </c>
-      <c r="I29" s="3">
-        <v>-200</v>
       </c>
       <c r="J29" s="3">
         <v>-200</v>
       </c>
       <c r="K29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L29" s="3">
         <v>13400</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-29100</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N29" s="3">
+      <c r="N29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O29" s="3">
         <v>-9200</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-9700</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -2116,8 +2177,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>5</v>
@@ -2125,8 +2186,11 @@
       <c r="X29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,61 +2328,64 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-300</v>
       </c>
       <c r="G32" s="3">
         <v>-300</v>
       </c>
       <c r="H32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-700</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-400</v>
       </c>
       <c r="U32" s="3">
         <v>-400</v>
@@ -2324,13 +2394,16 @@
         <v>-400</v>
       </c>
       <c r="W32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="X32" s="3">
         <v>-500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2338,67 +2411,70 @@
         <v>-6200</v>
       </c>
       <c r="E33" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-6600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-73300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-21300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-19900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-20600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-23200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-24700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-167400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-40200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-21500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-23200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-19000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-15200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,8 +2541,11 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2474,140 +2553,146 @@
         <v>-6200</v>
       </c>
       <c r="E35" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-6600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-73300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-21300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-19900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-20600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-23200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-24700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-167400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-40200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-21500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-23200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-19000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-15200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,76 +2744,80 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E41" s="3">
         <v>30600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>15400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>20600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>30200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>30900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>35500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>42800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>50500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>42300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>52300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>103400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>118500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>57600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>73000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>96500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>57600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>43800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>34200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>65100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>62000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>49500</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2780,90 +2870,96 @@
         <v>0</v>
       </c>
       <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
         <v>12100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>57100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>44400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>59600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3">
         <v>300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>15800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>11200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>10400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>8300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>100</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2888,39 +2984,39 @@
       <c r="J44" s="3">
         <v>0</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L44" s="3">
+      <c r="K44" s="3">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M44" s="3">
         <v>7300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>7400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1400</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2930,144 +3026,153 @@
       <c r="X44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>71200</v>
+      </c>
+      <c r="E45" s="3">
         <v>65300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>29300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>19100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2100</v>
-      </c>
-      <c r="V45" s="3">
-        <v>3700</v>
       </c>
       <c r="W45" s="3">
         <v>3700</v>
       </c>
       <c r="X45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="Y45" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>90200</v>
+      </c>
+      <c r="E46" s="3">
         <v>96000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>17500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>23000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>33000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>38300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>44000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>51900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>60700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>63200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>76100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>128400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>143100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>87300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>98200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>119300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>98400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>76400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>93400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>113100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>125200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>139500</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3119,31 +3224,34 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U47" s="3">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V47" s="3">
         <v>2000</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
         <v>200</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>5</v>
+      <c r="E48" s="3">
+        <v>200</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>5</v>
@@ -3151,59 +3259,62 @@
       <c r="G48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H48" s="3">
-        <v>0</v>
+      <c r="H48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I48" s="3">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3">
         <v>100</v>
-      </c>
-      <c r="J48" s="3">
-        <v>300</v>
       </c>
       <c r="K48" s="3">
         <v>300</v>
       </c>
       <c r="L48" s="3">
+        <v>300</v>
+      </c>
+      <c r="M48" s="3">
         <v>400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5400</v>
-      </c>
-      <c r="S48" s="3">
-        <v>4600</v>
       </c>
       <c r="T48" s="3">
         <v>4600</v>
       </c>
       <c r="U48" s="3">
+        <v>4600</v>
+      </c>
+      <c r="V48" s="3">
         <v>900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3246,20 +3357,20 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>5</v>
+      <c r="Q49" s="3">
+        <v>0</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S49" s="3">
+      <c r="S49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T49" s="3">
         <v>4000</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
-      </c>
-      <c r="U49" s="3" t="s">
-        <v>5</v>
+      <c r="U49" s="3">
+        <v>0</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>5</v>
@@ -3270,8 +3381,11 @@
       <c r="X49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,76 +3523,82 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E52" s="3">
         <v>1500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>53500</v>
-      </c>
-      <c r="T52" s="3">
-        <v>200</v>
       </c>
       <c r="U52" s="3">
         <v>200</v>
       </c>
       <c r="V52" s="3">
+        <v>200</v>
+      </c>
+      <c r="W52" s="3">
         <v>100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,76 +3665,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>91700</v>
+      </c>
+      <c r="E54" s="3">
         <v>97700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>19300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>25000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>35300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>40800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>46900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>55200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>64300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>67000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>81300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>134000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>149200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>93700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>107700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>130800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>160500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>81200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>96600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>114400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>126300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>139900</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,76 +3792,80 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E57" s="3">
         <v>1700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>14100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>19400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3766,11 +3900,11 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>33400</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>5</v>
       </c>
@@ -3786,8 +3920,8 @@
       <c r="T58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -3798,144 +3932,153 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E59" s="3">
         <v>5900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>18100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>18600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>14300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>42500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>16900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E60" s="3">
         <v>7500</v>
-      </c>
-      <c r="E60" s="3">
-        <v>6400</v>
       </c>
       <c r="F60" s="3">
         <v>6400</v>
       </c>
       <c r="G60" s="3">
+        <v>6400</v>
+      </c>
+      <c r="H60" s="3">
         <v>7500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9300</v>
-      </c>
-      <c r="I60" s="3">
-        <v>6800</v>
       </c>
       <c r="J60" s="3">
         <v>6800</v>
       </c>
       <c r="K60" s="3">
+        <v>6800</v>
+      </c>
+      <c r="L60" s="3">
         <v>8600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>21000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>57600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>21500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>21800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>23200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>24200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>56600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>29300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3973,26 +4116,26 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>33300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>33200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>33000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>32900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>32800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>32700</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4002,8 +4145,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4011,7 +4157,7 @@
         <v>1400</v>
       </c>
       <c r="E62" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="F62" s="3">
         <v>1300</v>
@@ -4019,8 +4165,8 @@
       <c r="G62" s="3">
         <v>1300</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>5</v>
+      <c r="H62" s="3">
+        <v>1300</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>5</v>
@@ -4031,47 +4177,50 @@
       <c r="K62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3">
         <v>1400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>300</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
-      </c>
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,76 +4429,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E66" s="3">
         <v>9000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9300</v>
-      </c>
-      <c r="I66" s="3">
-        <v>6800</v>
       </c>
       <c r="J66" s="3">
         <v>6800</v>
       </c>
       <c r="K66" s="3">
+        <v>6800</v>
+      </c>
+      <c r="L66" s="3">
         <v>8600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>22400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>59100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>56300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>56200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>58200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>59300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>91000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>63600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>12200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>10600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4522,11 +4690,11 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
         <v>200</v>
       </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
       <c r="J70" s="3">
         <v>0</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,76 +4811,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-697600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-691300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-685100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-678600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-668500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-662700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-652800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-643300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-634900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-639500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-628000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-606700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-586700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-566200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-543000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-518300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-350900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-310600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-162800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-146000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-129500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-110600</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,76 +5095,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>83400</v>
+      </c>
+      <c r="E76" s="3">
         <v>88700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>17300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>26400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>31200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>40100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>48400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>55700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>48600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>58900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>74900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>92900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>37500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>49500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>71500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>69500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>17600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>87000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>102200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>115600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>130400</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,81 +5237,87 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5130,67 +5325,70 @@
         <v>-6200</v>
       </c>
       <c r="E81" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-6600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-73300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-21300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-19900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-20600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-23200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-24700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-167400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-40200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-21500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-23200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-19000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-15200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,13 +5413,14 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
@@ -5233,23 +5432,23 @@
         <v>0</v>
       </c>
       <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
         <v>-200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>200</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
       <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
@@ -5257,7 +5456,7 @@
         <v>0</v>
       </c>
       <c r="P83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q83" s="3">
         <v>100</v>
@@ -5269,10 +5468,10 @@
         <v>100</v>
       </c>
       <c r="T83" s="3">
+        <v>100</v>
+      </c>
+      <c r="U83" s="3">
         <v>-200</v>
-      </c>
-      <c r="U83" s="3">
-        <v>100</v>
       </c>
       <c r="V83" s="3">
         <v>100</v>
@@ -5281,10 +5480,13 @@
         <v>100</v>
       </c>
       <c r="X83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +5837,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-9600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-9200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-9000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-56400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-17500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-16300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-12600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-25400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-23600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-35900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-52200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-16400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-19300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-12700</v>
-      </c>
-      <c r="W89" s="3">
-        <v>-16600</v>
       </c>
       <c r="X89" s="3">
         <v>-16600</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3">
+        <v>-16600</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,8 +5937,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5744,7 +5965,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L91" s="3">
         <v>-100</v>
@@ -5753,7 +5974,7 @@
         <v>-100</v>
       </c>
       <c r="N91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -5765,11 +5986,11 @@
         <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
@@ -5785,8 +6006,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,76 +6148,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-62400</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>5000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>16700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1000</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>1000</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>2000</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>21100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>66000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>5500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-7100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>15400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>27500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,76 +6530,82 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>82700</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>200</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>39800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-33600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>73500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>8000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>53600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-23000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>23000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3000</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6408,11 +6657,11 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
@@ -6420,75 +6669,81 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="E102" s="3">
         <v>15200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-9600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-7200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-8300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>8200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-15600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-51100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-15400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>61000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-15400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-23600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>38900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>13900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-31400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>12400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-20700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VYNE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VYNE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
   <si>
     <t>VYNE</t>
   </si>
@@ -656,119 +656,123 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E8" s="3">
         <v>100</v>
@@ -783,44 +787,44 @@
         <v>100</v>
       </c>
       <c r="I8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
         <v>200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1800</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
       <c r="V8" s="3">
         <v>0</v>
       </c>
@@ -828,13 +832,16 @@
         <v>0</v>
       </c>
       <c r="X8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
         <v>300</v>
       </c>
-      <c r="Y8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -865,33 +872,33 @@
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" s="3">
         <v>900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>300</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>5</v>
       </c>
@@ -904,8 +911,11 @@
       <c r="Y9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -936,33 +946,33 @@
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M10" s="3">
-        <v>0</v>
+      <c r="M10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N10" s="3">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3">
         <v>3100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>11500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1500</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>5</v>
       </c>
@@ -975,8 +985,11 @@
       <c r="Y10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,79 +1015,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E12" s="3">
         <v>3700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>19500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>7000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>4300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>6600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>16000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>11800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>12500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>12600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>10800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,8 +1161,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1215,8 +1235,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1286,8 +1309,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1336,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E17" s="3">
         <v>7500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>39800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>21900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>26300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>26800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>178900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>41600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>21900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>23200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>19400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>16200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-6800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-6200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-10400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-9300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-38900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-17800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-9500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-22000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-23500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-167200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-39800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-21900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-23200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-19400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-15900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-18400</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,64 +1512,65 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>1100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>300</v>
       </c>
       <c r="H20" s="3">
         <v>300</v>
       </c>
       <c r="I20" s="3">
+        <v>300</v>
+      </c>
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>700</v>
-      </c>
-      <c r="U20" s="3">
-        <v>400</v>
       </c>
       <c r="V20" s="3">
         <v>400</v>
@@ -1545,84 +1579,90 @@
         <v>400</v>
       </c>
       <c r="X20" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y20" s="3">
         <v>500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-6200</v>
+        <v>-9400</v>
       </c>
       <c r="E21" s="3">
         <v>-6200</v>
       </c>
       <c r="F21" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="G21" s="3">
         <v>-6100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-10000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-5600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-7900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-9100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-38900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-17800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-9600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-21900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-23600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-166500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-39100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-21700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-22700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-18900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-15300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1632,17 +1672,17 @@
       <c r="E22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>5</v>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1654,22 +1694,22 @@
         <v>0</v>
       </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>5600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>3500</v>
-      </c>
-      <c r="O22" s="3">
-        <v>1100</v>
       </c>
       <c r="P22" s="3">
         <v>1100</v>
       </c>
       <c r="Q22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="R22" s="3">
         <v>1200</v>
-      </c>
-      <c r="R22" s="3">
-        <v>1100</v>
       </c>
       <c r="S22" s="3">
         <v>1100</v>
@@ -1677,99 +1717,105 @@
       <c r="T22" s="3">
         <v>1100</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V22" s="3">
+      <c r="U22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W22" s="3">
         <v>300</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
       <c r="X22" s="3">
         <v>0</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-6200</v>
+        <v>-9400</v>
       </c>
       <c r="E23" s="3">
         <v>-6200</v>
       </c>
       <c r="F23" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="G23" s="3">
         <v>-6100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-9300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-44700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-21300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-10700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-23200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-24700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-167700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-40200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-21500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-23200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-19000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-15400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1796,11 +1842,11 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-400</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -1814,28 +1860,31 @@
         <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>-300</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>-200</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1954,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-6200</v>
+        <v>-9400</v>
       </c>
       <c r="E26" s="3">
         <v>-6200</v>
       </c>
       <c r="F26" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="G26" s="3">
         <v>-6100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-8200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-8700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-44200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-21300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-10700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-23200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-24700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-167400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-40200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-21500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-23200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-19000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-15200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-6200</v>
+        <v>-9400</v>
       </c>
       <c r="E27" s="3">
         <v>-6200</v>
       </c>
       <c r="F27" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="G27" s="3">
         <v>-6100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-8700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-44200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-21300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-10700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-23200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-24700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-167400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-40200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-21500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-23200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-19000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-15200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2130,43 +2191,43 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>-500</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-2200</v>
-      </c>
-      <c r="J29" s="3">
-        <v>-200</v>
       </c>
       <c r="K29" s="3">
         <v>-200</v>
       </c>
       <c r="L29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M29" s="3">
         <v>13400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-29100</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O29" s="3">
+      <c r="O29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P29" s="3">
         <v>-9200</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-9700</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2180,8 +2241,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
@@ -2189,8 +2250,11 @@
       <c r="Y29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,64 +2398,67 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-300</v>
       </c>
       <c r="H32" s="3">
         <v>-300</v>
       </c>
       <c r="I32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-700</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-400</v>
       </c>
       <c r="V32" s="3">
         <v>-400</v>
@@ -2397,84 +2467,90 @@
         <v>-400</v>
       </c>
       <c r="X32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-6200</v>
+        <v>-9400</v>
       </c>
       <c r="E33" s="3">
         <v>-6200</v>
       </c>
       <c r="F33" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="G33" s="3">
         <v>-6600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-73300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-21300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-19900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-23200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-24700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-167400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-40200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-21500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-23200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-19000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-15200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-6200</v>
+        <v>-9400</v>
       </c>
       <c r="E35" s="3">
         <v>-6200</v>
       </c>
       <c r="F35" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="G35" s="3">
         <v>-6600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-73300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-21300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-19900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-23200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-24700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-167400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-40200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-21500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-23200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-19000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-15200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,79 +2831,83 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E41" s="3">
         <v>19100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>30600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>15400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>30200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>30900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>35500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>42800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>50500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>42300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>52300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>103400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>118500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>57600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>73000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>96500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>57600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>43800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>34200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>65100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>62000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>49500</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2873,93 +2963,99 @@
         <v>0</v>
       </c>
       <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
         <v>12100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>57100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>44400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>59600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E43" s="3">
-        <v>0</v>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F43" s="3">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3">
         <v>300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>15800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>11200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>10400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>8300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>100</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2987,39 +3083,39 @@
       <c r="K44" s="3">
         <v>0</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N44" s="3">
         <v>7300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>7400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>6700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1400</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W44" s="3" t="s">
         <v>5</v>
       </c>
@@ -3029,150 +3125,159 @@
       <c r="Y44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>54200</v>
+      </c>
+      <c r="E45" s="3">
         <v>71200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>65300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>7400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>29300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>19100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2100</v>
-      </c>
-      <c r="W45" s="3">
-        <v>3700</v>
       </c>
       <c r="X45" s="3">
         <v>3700</v>
       </c>
       <c r="Y45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="Z45" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>83800</v>
+      </c>
+      <c r="E46" s="3">
         <v>90200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>96000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>17500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>23000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>33000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>38300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>44000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>51900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>60700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>63200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>76100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>128400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>143100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>87300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>98200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>119300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>98400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>76400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>93400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>113100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>125200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>139500</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3227,23 +3332,26 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V47" s="3">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W47" s="3">
         <v>2000</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3253,8 +3361,8 @@
       <c r="E48" s="3">
         <v>200</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>5</v>
+      <c r="F48" s="3">
+        <v>200</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>5</v>
@@ -3262,59 +3370,62 @@
       <c r="H48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I48" s="3">
-        <v>0</v>
+      <c r="I48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J48" s="3">
+        <v>0</v>
+      </c>
+      <c r="K48" s="3">
         <v>100</v>
-      </c>
-      <c r="K48" s="3">
-        <v>300</v>
       </c>
       <c r="L48" s="3">
         <v>300</v>
       </c>
       <c r="M48" s="3">
+        <v>300</v>
+      </c>
+      <c r="N48" s="3">
         <v>400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5400</v>
-      </c>
-      <c r="T48" s="3">
-        <v>4600</v>
       </c>
       <c r="U48" s="3">
         <v>4600</v>
       </c>
       <c r="V48" s="3">
+        <v>4600</v>
+      </c>
+      <c r="W48" s="3">
         <v>900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3360,20 +3471,20 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>5</v>
+      <c r="R49" s="3">
+        <v>0</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T49" s="3">
+      <c r="T49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U49" s="3">
         <v>4000</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
-      </c>
-      <c r="V49" s="3" t="s">
-        <v>5</v>
+      <c r="V49" s="3">
+        <v>0</v>
       </c>
       <c r="W49" s="3" t="s">
         <v>5</v>
@@ -3384,8 +3495,11 @@
       <c r="Y49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,79 +3643,85 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E52" s="3">
         <v>1300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>53500</v>
-      </c>
-      <c r="U52" s="3">
-        <v>200</v>
       </c>
       <c r="V52" s="3">
         <v>200</v>
       </c>
       <c r="W52" s="3">
+        <v>200</v>
+      </c>
+      <c r="X52" s="3">
         <v>100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,79 +3791,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>86600</v>
+      </c>
+      <c r="E54" s="3">
         <v>91700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>97700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>19300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>25000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>35300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>40800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>46900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>55200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>64300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>67000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>81300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>134000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>149200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>93700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>107700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>130800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>160500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>81200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>96600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>114400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>126300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>139900</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,79 +3923,83 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E57" s="3">
         <v>2800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>14100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>19400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3903,11 +4037,11 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>33400</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>5</v>
       </c>
@@ -3923,8 +4057,8 @@
       <c r="U58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -3935,150 +4069,159 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E59" s="3">
         <v>4100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>17000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>18600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>14300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>42500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>16900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>7200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E60" s="3">
         <v>6900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7500</v>
-      </c>
-      <c r="F60" s="3">
-        <v>6400</v>
       </c>
       <c r="G60" s="3">
         <v>6400</v>
       </c>
       <c r="H60" s="3">
+        <v>6400</v>
+      </c>
+      <c r="I60" s="3">
         <v>7500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9300</v>
-      </c>
-      <c r="J60" s="3">
-        <v>6800</v>
       </c>
       <c r="K60" s="3">
         <v>6800</v>
       </c>
       <c r="L60" s="3">
+        <v>6800</v>
+      </c>
+      <c r="M60" s="3">
         <v>8600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>18400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>21000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>57600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>21500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>21800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>23200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>24200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>56600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>29300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>11900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4119,26 +4262,26 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>33300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>33200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>33000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>32900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>32800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>32700</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4148,19 +4291,22 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="E62" s="3">
         <v>1400</v>
       </c>
       <c r="F62" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="G62" s="3">
         <v>1300</v>
@@ -4168,8 +4314,8 @@
       <c r="H62" s="3">
         <v>1300</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>5</v>
+      <c r="I62" s="3">
+        <v>1300</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>5</v>
@@ -4180,47 +4326,50 @@
       <c r="L62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
         <v>1400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>300</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
-      </c>
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,79 +4587,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E66" s="3">
         <v>8300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9300</v>
-      </c>
-      <c r="J66" s="3">
-        <v>6800</v>
       </c>
       <c r="K66" s="3">
         <v>6800</v>
       </c>
       <c r="L66" s="3">
+        <v>6800</v>
+      </c>
+      <c r="M66" s="3">
         <v>8600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>22400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>59100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>56300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>56200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>58200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>59300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>91000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>63600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>12200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>10600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4693,11 +4861,11 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
         <v>200</v>
       </c>
-      <c r="J70" s="3">
-        <v>0</v>
-      </c>
       <c r="K70" s="3">
         <v>0</v>
       </c>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,79 +4985,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-707000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-697600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-691300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-685100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-678600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-668500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-662700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-652800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-643300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-634900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-639500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-628000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-606700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-586700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-566200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-543000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-518300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-350900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-310600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-162800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-146000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-129500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-110600</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,79 +5281,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>74900</v>
+      </c>
+      <c r="E76" s="3">
         <v>83400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>88700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>26400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>31200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>40100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>48400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>55700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>48600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>58900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>74900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>92900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>37500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>49500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>71500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>69500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>17600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>87000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>102200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>115600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>130400</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-6200</v>
+        <v>-9400</v>
       </c>
       <c r="E81" s="3">
         <v>-6200</v>
       </c>
       <c r="F81" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="G81" s="3">
         <v>-6600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-73300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-21300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-19900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-23200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-24700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-167400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-40200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-21500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-23200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-19000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-15200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,16 +5612,17 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -5435,23 +5634,23 @@
         <v>0</v>
       </c>
       <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
         <v>-200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>200</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
       <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
@@ -5459,7 +5658,7 @@
         <v>0</v>
       </c>
       <c r="Q83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R83" s="3">
         <v>100</v>
@@ -5471,10 +5670,10 @@
         <v>100</v>
       </c>
       <c r="U83" s="3">
+        <v>100</v>
+      </c>
+      <c r="V83" s="3">
         <v>-200</v>
-      </c>
-      <c r="V83" s="3">
-        <v>100</v>
       </c>
       <c r="W83" s="3">
         <v>100</v>
@@ -5483,10 +5682,13 @@
         <v>100</v>
       </c>
       <c r="Y83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6054,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-9600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-9200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-9000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-56400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-17500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-16300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-25400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-23600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-35900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-52200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-16400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-19300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-12700</v>
-      </c>
-      <c r="X89" s="3">
-        <v>-16600</v>
       </c>
       <c r="Y89" s="3">
         <v>-16600</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3">
+        <v>-16600</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,8 +6158,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5968,7 +6189,7 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
@@ -5977,7 +6198,7 @@
         <v>-100</v>
       </c>
       <c r="O91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -5989,11 +6210,11 @@
         <v>0</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
@@ -6009,8 +6230,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,79 +6378,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-62400</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>5000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>16700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1000</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>1000</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>2000</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>21100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>66000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>5500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-7100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>15400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>27500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6482,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6320,8 +6554,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,8 +6776,11 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6542,70 +6788,73 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>82700</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>39800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-33600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>73500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>8000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>53600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-23000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>23000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3000</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6660,11 +6909,11 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
@@ -6672,78 +6921,84 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>15200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>8200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-15600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-51100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-15400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>61000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-15400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-23600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>38900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>13900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-31400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>12400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-20700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VYNE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VYNE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
   <si>
     <t>VYNE</t>
   </si>
@@ -656,126 +656,130 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>100</v>
+      </c>
+      <c r="E8" s="3">
         <v>200</v>
-      </c>
-      <c r="E8" s="3">
-        <v>100</v>
       </c>
       <c r="F8" s="3">
         <v>100</v>
@@ -790,44 +794,44 @@
         <v>100</v>
       </c>
       <c r="J8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
         <v>200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1800</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
-      </c>
       <c r="W8" s="3">
         <v>0</v>
       </c>
@@ -835,13 +839,16 @@
         <v>0</v>
       </c>
       <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
         <v>300</v>
       </c>
-      <c r="Z8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -875,33 +882,33 @@
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O9" s="3">
         <v>900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>300</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>5</v>
       </c>
@@ -914,31 +921,34 @@
       <c r="Z9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>200</v>
+      </c>
+      <c r="F10" s="3">
+        <v>100</v>
+      </c>
+      <c r="G10" s="3">
+        <v>100</v>
+      </c>
+      <c r="H10" s="3">
+        <v>100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>100</v>
+      </c>
+      <c r="J10" s="3">
+        <v>100</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -949,33 +959,33 @@
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N10" s="3">
-        <v>0</v>
+      <c r="N10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
         <v>3100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>11500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1500</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>5</v>
       </c>
@@ -988,8 +998,11 @@
       <c r="Z10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,82 +1029,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E12" s="3">
         <v>7300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>7200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>19500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>7000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>4300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>6600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>13100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>16000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>11800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>12500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>12600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>10800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,31 +1181,34 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1238,8 +1258,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1312,8 +1335,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,156 +1363,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E17" s="3">
         <v>10600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>10500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>39800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>21900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>10000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>26300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>26800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>178900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>41600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>21900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>23200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>19400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>16200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-10400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-7400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-6800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-6200</v>
       </c>
-      <c r="H18" s="3">
-        <v>-10400</v>
-      </c>
       <c r="I18" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="J18" s="3">
         <v>-5900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-9300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-38900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-17800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-9800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-22000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-23500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-167200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-39800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-21900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-23200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-19400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-15900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-18400</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,67 +1546,68 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>1000</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
+        <v>200</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>100</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U20" s="3">
+        <v>500</v>
+      </c>
+      <c r="V20" s="3">
         <v>700</v>
-      </c>
-      <c r="G20" s="3">
-        <v>200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>300</v>
-      </c>
-      <c r="J20" s="3">
-        <v>200</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="T20" s="3">
-        <v>500</v>
-      </c>
-      <c r="U20" s="3">
-        <v>700</v>
-      </c>
-      <c r="V20" s="3">
-        <v>400</v>
       </c>
       <c r="W20" s="3">
         <v>400</v>
@@ -1582,87 +1616,93 @@
         <v>400</v>
       </c>
       <c r="Y20" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z20" s="3">
         <v>500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-9400</v>
+        <v>-13100</v>
       </c>
       <c r="E21" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="H21" s="3">
         <v>-6200</v>
       </c>
-      <c r="F21" s="3">
-        <v>-6200</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-10000</v>
-      </c>
       <c r="I21" s="3">
-        <v>-5600</v>
+        <v>-10300</v>
       </c>
       <c r="J21" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="K21" s="3">
         <v>-7900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-9100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-8700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-38900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-17800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-9600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-9800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-21900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-23600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-166500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-39100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-21700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-22700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-18900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-15300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1675,8 +1715,8 @@
       <c r="F22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>5</v>
@@ -1684,8 +1724,8 @@
       <c r="I22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1697,22 +1737,22 @@
         <v>0</v>
       </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>5600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3500</v>
-      </c>
-      <c r="P22" s="3">
-        <v>1100</v>
       </c>
       <c r="Q22" s="3">
         <v>1100</v>
       </c>
       <c r="R22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="S22" s="3">
         <v>1200</v>
-      </c>
-      <c r="S22" s="3">
-        <v>1100</v>
       </c>
       <c r="T22" s="3">
         <v>1100</v>
@@ -1720,120 +1760,126 @@
       <c r="U22" s="3">
         <v>1100</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W22" s="3">
+      <c r="V22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X22" s="3">
         <v>300</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9400</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-6200</v>
       </c>
       <c r="F23" s="3">
         <v>-6200</v>
       </c>
       <c r="G23" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="H23" s="3">
         <v>-6100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-44700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-21300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-10900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-23200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-24700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-167700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-40200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-21500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-23200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-15400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1845,11 +1891,11 @@
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-400</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
@@ -1863,28 +1909,31 @@
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>-300</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W24" s="3">
-        <v>0</v>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X24" s="3">
         <v>0</v>
       </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-200</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2006,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9400</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-6200</v>
       </c>
       <c r="F26" s="3">
         <v>-6200</v>
       </c>
       <c r="G26" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="H26" s="3">
         <v>-6100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-10000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-8200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-44200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-21300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-10900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-23200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-24700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-167400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-40200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-21500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-23200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-15200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9400</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-6200</v>
       </c>
       <c r="F27" s="3">
         <v>-6200</v>
       </c>
       <c r="G27" s="3">
-        <v>-6100</v>
+        <v>-6300</v>
       </c>
       <c r="H27" s="3">
-        <v>-10000</v>
+        <v>-6600</v>
       </c>
       <c r="I27" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="J27" s="3">
         <v>-5600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-8200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-44200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-21300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-10900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-23200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-24700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-167400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-40200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-21500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-23200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-15200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2237,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2194,43 +2255,43 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-500</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-2200</v>
-      </c>
-      <c r="K29" s="3">
-        <v>-200</v>
       </c>
       <c r="L29" s="3">
         <v>-200</v>
       </c>
       <c r="M29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N29" s="3">
         <v>13400</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-29100</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P29" s="3">
+      <c r="P29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-9700</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="S29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
@@ -2244,8 +2305,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
@@ -2253,8 +2314,11 @@
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2391,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,67 +2468,70 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>100</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>100</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>200</v>
+      </c>
+      <c r="U32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="V32" s="3">
         <v>-700</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
-        <v>200</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-700</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-400</v>
       </c>
       <c r="W32" s="3">
         <v>-400</v>
@@ -2470,87 +2540,93 @@
         <v>-400</v>
       </c>
       <c r="Y32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9400</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-6200</v>
       </c>
       <c r="F33" s="3">
         <v>-6200</v>
       </c>
       <c r="G33" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="H33" s="3">
         <v>-6600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-8500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-73300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-21300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-19900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-20600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-23200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-24700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-167400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-40200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-21500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-23200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-15200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2699,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9400</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-6200</v>
       </c>
       <c r="F35" s="3">
         <v>-6200</v>
       </c>
       <c r="G35" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="H35" s="3">
         <v>-6600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-8500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-73300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-21300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-19900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-20600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-23200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-24700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-167400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-40200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-21500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-23200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-15200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2889,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,96 +2918,100 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E41" s="3">
         <v>29600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>19100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>30600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>20600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>30200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>30900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>35500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>42800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>50500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>42300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>52300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>103400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>118500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>57600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>73000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>96500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>57600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>43800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>34200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>65100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>62000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>49500</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>53900</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>48500</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>66900</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>62600</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
@@ -2966,22 +3056,25 @@
         <v>0</v>
       </c>
       <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
         <v>12100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>57100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>44400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>59600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2991,94 +3084,97 @@
       <c r="E43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3">
         <v>300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>15800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>11200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>10400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>100</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Y43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3086,39 +3182,39 @@
       <c r="L44" s="3">
         <v>0</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N44" s="3">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O44" s="3">
         <v>7300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>8100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>7400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>6700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1400</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>5</v>
       </c>
@@ -3128,179 +3224,188 @@
       <c r="Z44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>54200</v>
-      </c>
-      <c r="E45" s="3">
-        <v>71200</v>
-      </c>
-      <c r="F45" s="3">
-        <v>65300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1800</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K45" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L45" s="3">
+        <v>3100</v>
+      </c>
+      <c r="M45" s="3">
+        <v>3800</v>
+      </c>
+      <c r="N45" s="3">
+        <v>4600</v>
+      </c>
+      <c r="O45" s="3">
+        <v>6100</v>
+      </c>
+      <c r="P45" s="3">
+        <v>5700</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>5900</v>
+      </c>
+      <c r="R45" s="3">
+        <v>5800</v>
+      </c>
+      <c r="S45" s="3">
+        <v>6500</v>
+      </c>
+      <c r="T45" s="3">
+        <v>7400</v>
+      </c>
+      <c r="U45" s="3">
+        <v>6600</v>
+      </c>
+      <c r="V45" s="3">
+        <v>29300</v>
+      </c>
+      <c r="W45" s="3">
+        <v>19100</v>
+      </c>
+      <c r="X45" s="3">
         <v>2100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J45" s="3">
-        <v>2200</v>
-      </c>
-      <c r="K45" s="3">
-        <v>3100</v>
-      </c>
-      <c r="L45" s="3">
-        <v>3800</v>
-      </c>
-      <c r="M45" s="3">
-        <v>4600</v>
-      </c>
-      <c r="N45" s="3">
-        <v>6100</v>
-      </c>
-      <c r="O45" s="3">
-        <v>5700</v>
-      </c>
-      <c r="P45" s="3">
-        <v>5900</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>5800</v>
-      </c>
-      <c r="R45" s="3">
-        <v>6500</v>
-      </c>
-      <c r="S45" s="3">
-        <v>7400</v>
-      </c>
-      <c r="T45" s="3">
-        <v>6600</v>
-      </c>
-      <c r="U45" s="3">
-        <v>29300</v>
-      </c>
-      <c r="V45" s="3">
-        <v>19100</v>
-      </c>
-      <c r="W45" s="3">
-        <v>2100</v>
-      </c>
-      <c r="X45" s="3">
-        <v>3700</v>
       </c>
       <c r="Y45" s="3">
         <v>3700</v>
       </c>
       <c r="Z45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AA45" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>73500</v>
+      </c>
+      <c r="E46" s="3">
         <v>83800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>90200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>96000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>17500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>23000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>33000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>38300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>44000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>51900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>60700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>63200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>76100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>128400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>143100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>87300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>98200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>119300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>98400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>76400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>93400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>113100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>125200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>139500</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3335,28 +3440,31 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W47" s="3">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X47" s="3">
         <v>2000</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E48" s="3">
         <v>200</v>
@@ -3364,8 +3472,8 @@
       <c r="F48" s="3">
         <v>200</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>5</v>
+      <c r="G48" s="3">
+        <v>200</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>5</v>
@@ -3373,59 +3481,62 @@
       <c r="I48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J48" s="3">
-        <v>0</v>
+      <c r="J48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K48" s="3">
+        <v>0</v>
+      </c>
+      <c r="L48" s="3">
         <v>100</v>
-      </c>
-      <c r="L48" s="3">
-        <v>300</v>
       </c>
       <c r="M48" s="3">
         <v>300</v>
       </c>
       <c r="N48" s="3">
+        <v>300</v>
+      </c>
+      <c r="O48" s="3">
         <v>400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5400</v>
-      </c>
-      <c r="U48" s="3">
-        <v>4600</v>
       </c>
       <c r="V48" s="3">
         <v>4600</v>
       </c>
       <c r="W48" s="3">
+        <v>4600</v>
+      </c>
+      <c r="X48" s="3">
         <v>900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3474,20 +3585,20 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>5</v>
+      <c r="S49" s="3">
+        <v>0</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U49" s="3">
+      <c r="U49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V49" s="3">
         <v>4000</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
-      </c>
-      <c r="W49" s="3" t="s">
-        <v>5</v>
+      <c r="W49" s="3">
+        <v>0</v>
       </c>
       <c r="X49" s="3" t="s">
         <v>5</v>
@@ -3498,8 +3609,11 @@
       <c r="Z49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3686,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,82 +3763,88 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E52" s="3">
         <v>2700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>53500</v>
-      </c>
-      <c r="V52" s="3">
-        <v>200</v>
       </c>
       <c r="W52" s="3">
         <v>200</v>
       </c>
       <c r="X52" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y52" s="3">
         <v>100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,82 +3917,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>76200</v>
+      </c>
+      <c r="E54" s="3">
         <v>86600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>91700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>97700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>19300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>25000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>35300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>40800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>46900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>55200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>64300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>67000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>81300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>134000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>149200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>93700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>107700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>130800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>160500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>81200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>96600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>114400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>126300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>139900</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4025,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,96 +4054,100 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>14100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>19400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -4040,11 +4174,11 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>33400</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>5</v>
       </c>
@@ -4060,8 +4194,8 @@
       <c r="V58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -4072,156 +4206,165 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="G59" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K59" s="3">
+        <v>7000</v>
+      </c>
+      <c r="L59" s="3">
+        <v>4300</v>
+      </c>
+      <c r="M59" s="3">
+        <v>5400</v>
+      </c>
+      <c r="N59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="O59" s="3">
+        <v>11900</v>
+      </c>
+      <c r="P59" s="3">
+        <v>13400</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>14200</v>
+      </c>
+      <c r="R59" s="3">
+        <v>18100</v>
+      </c>
+      <c r="S59" s="3">
+        <v>17000</v>
+      </c>
+      <c r="T59" s="3">
+        <v>18600</v>
+      </c>
+      <c r="U59" s="3">
+        <v>14300</v>
+      </c>
+      <c r="V59" s="3">
+        <v>42500</v>
+      </c>
+      <c r="W59" s="3">
+        <v>16900</v>
+      </c>
+      <c r="X59" s="3">
+        <v>6500</v>
+      </c>
+      <c r="Y59" s="3">
         <v>7200</v>
       </c>
-      <c r="E59" s="3">
-        <v>4100</v>
-      </c>
-      <c r="F59" s="3">
-        <v>5900</v>
-      </c>
-      <c r="G59" s="3">
-        <v>5700</v>
-      </c>
-      <c r="H59" s="3">
-        <v>5200</v>
-      </c>
-      <c r="I59" s="3">
-        <v>5300</v>
-      </c>
-      <c r="J59" s="3">
-        <v>7000</v>
-      </c>
-      <c r="K59" s="3">
-        <v>4300</v>
-      </c>
-      <c r="L59" s="3">
-        <v>5400</v>
-      </c>
-      <c r="M59" s="3">
-        <v>5000</v>
-      </c>
-      <c r="N59" s="3">
-        <v>11900</v>
-      </c>
-      <c r="O59" s="3">
-        <v>13400</v>
-      </c>
-      <c r="P59" s="3">
-        <v>14200</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>18100</v>
-      </c>
-      <c r="R59" s="3">
-        <v>17000</v>
-      </c>
-      <c r="S59" s="3">
-        <v>18600</v>
-      </c>
-      <c r="T59" s="3">
-        <v>14300</v>
-      </c>
-      <c r="U59" s="3">
-        <v>42500</v>
-      </c>
-      <c r="V59" s="3">
-        <v>16900</v>
-      </c>
-      <c r="W59" s="3">
-        <v>6500</v>
-      </c>
-      <c r="X59" s="3">
-        <v>7200</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E60" s="3">
         <v>11800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7500</v>
-      </c>
-      <c r="G60" s="3">
-        <v>6400</v>
       </c>
       <c r="H60" s="3">
         <v>6400</v>
       </c>
       <c r="I60" s="3">
+        <v>6400</v>
+      </c>
+      <c r="J60" s="3">
         <v>7500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9300</v>
-      </c>
-      <c r="K60" s="3">
-        <v>6800</v>
       </c>
       <c r="L60" s="3">
         <v>6800</v>
       </c>
       <c r="M60" s="3">
+        <v>6800</v>
+      </c>
+      <c r="N60" s="3">
         <v>8600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>18400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>21000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>57600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>21500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>21800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>23200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>24200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>56600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>29300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>11900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>10600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4232,10 +4375,10 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -4265,26 +4408,26 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>33300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>33200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>33000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>32900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>32800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>32700</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4294,19 +4437,22 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1400</v>
+      <c r="D62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F62" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="G62" s="3">
         <v>1300</v>
@@ -4317,8 +4463,8 @@
       <c r="I62" s="3">
         <v>1300</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>5</v>
+      <c r="J62" s="3">
+        <v>1300</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>5</v>
@@ -4329,47 +4475,50 @@
       <c r="M62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
+      <c r="N62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
         <v>1400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>300</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
-      </c>
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4591,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4668,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,82 +4745,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E66" s="3">
         <v>11800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9300</v>
-      </c>
-      <c r="K66" s="3">
-        <v>6800</v>
       </c>
       <c r="L66" s="3">
         <v>6800</v>
       </c>
       <c r="M66" s="3">
+        <v>6800</v>
+      </c>
+      <c r="N66" s="3">
         <v>8600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>22400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>59100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>56300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>56200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>58200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>59300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>91000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>63600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>12200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>10600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4853,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4928,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5005,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4864,11 +5032,11 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
         <v>200</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
       <c r="L70" s="3">
         <v>0</v>
       </c>
@@ -4914,8 +5082,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,82 +5159,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-719100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-707000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-697600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-691300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-685100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-678600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-668500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-662700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-652800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-643300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-634900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-639500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-628000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-606700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-586700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-566200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-543000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-518300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-350900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-310600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-162800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-146000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-129500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-110600</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5313,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5390,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,82 +5467,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>63500</v>
+      </c>
+      <c r="E76" s="3">
         <v>74900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>83400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>88700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>17300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>26400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>31200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>40100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>48400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>55700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>48600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>58900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>74900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>92900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>37500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>49500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>71500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>69500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>17600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>87000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>102200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>115600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>130400</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5621,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9400</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-6200</v>
       </c>
       <c r="F81" s="3">
         <v>-6200</v>
       </c>
       <c r="G81" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="H81" s="3">
         <v>-6600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-8500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-73300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-21300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-19900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-20600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-23200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-24700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-167400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-40200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-21500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-23200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-15200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,8 +5811,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5624,36 +5823,36 @@
       <c r="E83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
+      <c r="F83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I83" s="3">
         <v>0</v>
       </c>
       <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
         <v>-200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
       <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
         <v>100</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
       <c r="P83" s="3">
         <v>0</v>
       </c>
@@ -5661,7 +5860,7 @@
         <v>0</v>
       </c>
       <c r="R83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S83" s="3">
         <v>100</v>
@@ -5673,10 +5872,10 @@
         <v>100</v>
       </c>
       <c r="V83" s="3">
+        <v>100</v>
+      </c>
+      <c r="W83" s="3">
         <v>-200</v>
-      </c>
-      <c r="W83" s="3">
-        <v>100</v>
       </c>
       <c r="X83" s="3">
         <v>100</v>
@@ -5685,10 +5884,13 @@
         <v>100</v>
       </c>
       <c r="Z83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5963,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6040,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6117,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6194,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,8 +6271,11 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6066,73 +6283,76 @@
         <v>-8500</v>
       </c>
       <c r="E89" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-8000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-9600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-9200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-56400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-17500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-16300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-12600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-25400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-23600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-35900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-52200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-16400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-19300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-12700</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>-16600</v>
       </c>
       <c r="Z89" s="3">
         <v>-16600</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3">
+        <v>-16600</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,31 +6379,32 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -6192,7 +6413,7 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
@@ -6201,7 +6422,7 @@
         <v>-100</v>
       </c>
       <c r="P91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -6213,11 +6434,11 @@
         <v>0</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
@@ -6233,8 +6454,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6531,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,82 +6608,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E94" s="3">
         <v>19000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-62400</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>5000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>16700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1000</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>1000</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>2000</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>21100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>66000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>5500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-7100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>15400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>27500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,31 +6716,32 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6557,8 +6791,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6868,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6945,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,8 +7022,11 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6791,93 +7037,96 @@
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>82700</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>200</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>39800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-33600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>73500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>8000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>53600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-23000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>23000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>3000</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6912,11 +7161,11 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W101" s="3">
-        <v>0</v>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X101" s="3">
         <v>0</v>
@@ -6924,81 +7173,87 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E102" s="3">
         <v>10500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>15200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>8200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-15600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-51100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-15400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>61000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-15400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-23600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>38900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>13900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-31400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>12400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-20700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VYNE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VYNE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="92">
   <si>
     <t>VYNE</t>
   </si>
@@ -656,133 +656,136 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3">
         <v>100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>200</v>
-      </c>
-      <c r="F8" s="3">
-        <v>100</v>
       </c>
       <c r="G8" s="3">
         <v>100</v>
@@ -797,44 +800,44 @@
         <v>100</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
         <v>200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1800</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
       <c r="X8" s="3">
         <v>0</v>
       </c>
@@ -842,13 +845,16 @@
         <v>0</v>
       </c>
       <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="3">
         <v>300</v>
       </c>
-      <c r="AA8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -885,33 +891,33 @@
       <c r="N9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3">
         <v>900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>300</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>5</v>
       </c>
@@ -924,8 +930,11 @@
       <c r="AA9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -933,10 +942,10 @@
         <v>100</v>
       </c>
       <c r="E10" s="3">
+        <v>100</v>
+      </c>
+      <c r="F10" s="3">
         <v>200</v>
-      </c>
-      <c r="F10" s="3">
-        <v>100</v>
       </c>
       <c r="G10" s="3">
         <v>100</v>
@@ -950,8 +959,8 @@
       <c r="J10" s="3">
         <v>100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
+      <c r="K10" s="3">
+        <v>100</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
@@ -962,33 +971,33 @@
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O10" s="3">
-        <v>0</v>
+      <c r="O10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
         <v>3100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>11500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1500</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1001,8 +1010,11 @@
       <c r="AA10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1030,85 +1042,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E12" s="3">
         <v>10200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>19500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>7000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>4300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>6600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>13100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>16000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>11800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>12500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>12600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>10800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,8 +1200,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1210,8 +1229,8 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1261,8 +1280,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1338,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E17" s="3">
         <v>13200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>10500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>39800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>21900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>10000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>26300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>26800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>178900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>41600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>21900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>23200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>19400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>16200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-13100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-10400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-7400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-6800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-6200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-10300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-9300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-38900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-17800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-9500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-9800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-22000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-23500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-167200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-39800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-21900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-23200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-19400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-15900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-18400</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,8 +1579,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1573,44 +1606,44 @@
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>700</v>
-      </c>
-      <c r="W20" s="3">
-        <v>400</v>
       </c>
       <c r="X20" s="3">
         <v>400</v>
@@ -1619,90 +1652,96 @@
         <v>400</v>
       </c>
       <c r="Z20" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA20" s="3">
         <v>500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-13100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-10400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-7400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-6800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-6200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-10300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-5900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-7900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-9100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-8200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-8700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-38900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-17800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-9600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-9800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-21900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-23600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-166500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-39100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-21700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-22700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-18900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-15300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1727,8 +1766,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1740,22 +1779,22 @@
         <v>0</v>
       </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>5600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3500</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>1100</v>
       </c>
       <c r="R22" s="3">
         <v>1100</v>
       </c>
       <c r="S22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T22" s="3">
         <v>1200</v>
-      </c>
-      <c r="T22" s="3">
-        <v>1100</v>
       </c>
       <c r="U22" s="3">
         <v>1100</v>
@@ -1763,105 +1802,111 @@
       <c r="V22" s="3">
         <v>1100</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X22" s="3">
+      <c r="W22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y22" s="3">
         <v>300</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-12200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9400</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-6200</v>
       </c>
       <c r="G23" s="3">
         <v>-6200</v>
       </c>
       <c r="H23" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="I23" s="3">
         <v>-6100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-10000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-8700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-44700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-21300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-10700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-10900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-23200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-24700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-167700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-40200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-21500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-23200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-15400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>5</v>
+      <c r="D24" s="3">
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>5</v>
@@ -1881,8 +1926,8 @@
       <c r="J24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1894,11 +1939,11 @@
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>-400</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
@@ -1912,28 +1957,31 @@
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>-300</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
-      <c r="W24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X24" s="3">
-        <v>0</v>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-200</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9400</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-6200</v>
       </c>
       <c r="G26" s="3">
         <v>-6200</v>
       </c>
       <c r="H26" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="I26" s="3">
         <v>-6100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-10000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-8700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-44200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-21300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-10700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-10900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-23200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-24700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-167400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-40200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-21500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-23200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-15200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-10100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-8700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-44200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-21300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-10700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-10900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-23200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-24700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-167400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-40200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-21500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-23200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-15200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2258,43 +2318,43 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-500</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-2200</v>
-      </c>
-      <c r="L29" s="3">
-        <v>-200</v>
       </c>
       <c r="M29" s="3">
         <v>-200</v>
       </c>
       <c r="N29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O29" s="3">
         <v>13400</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-29100</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R29" s="3">
         <v>-9200</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-9700</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
@@ -2308,8 +2368,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
@@ -2317,8 +2377,11 @@
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,8 +2537,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2497,44 +2566,44 @@
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-700</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-400</v>
       </c>
       <c r="X32" s="3">
         <v>-400</v>
@@ -2543,90 +2612,96 @@
         <v>-400</v>
       </c>
       <c r="Z32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9400</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-6200</v>
       </c>
       <c r="G33" s="3">
         <v>-6200</v>
       </c>
       <c r="H33" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="I33" s="3">
         <v>-6600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-10100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-73300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-21300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-19900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-20600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-23200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-24700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-167400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-40200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-21500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-23200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-15200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9400</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-6200</v>
       </c>
       <c r="G35" s="3">
         <v>-6200</v>
       </c>
       <c r="H35" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="I35" s="3">
         <v>-6600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-10100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-73300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-21300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-19900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-20600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-23200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-24700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-167400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-40200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-21500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-23200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-15200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,103 +3004,107 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E41" s="3">
         <v>16300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>29600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>19100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>30600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>20600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>30200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>30900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>35500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>42800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>50500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>42300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>52300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>103400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>118500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>57600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>73000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>96500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>57600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>43800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>34200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>65100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>62000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>49500</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E42" s="3">
         <v>53900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>48500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>66900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>62600</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -3059,22 +3148,25 @@
         <v>0</v>
       </c>
       <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
         <v>12100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>57100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>44400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>59600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3090,68 +3182,71 @@
       <c r="G43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3">
         <v>300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>10800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>15800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>11200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>10400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>8300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>100</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3176,8 +3271,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3185,39 +3280,39 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O44" s="3">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P44" s="3">
         <v>7300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>8300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>8100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>7400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>6700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1400</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>5</v>
       </c>
@@ -3227,8 +3322,11 @@
       <c r="AA44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3253,136 +3351,142 @@
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L45" s="3">
         <v>2200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>29300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>19100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2100</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>3700</v>
       </c>
       <c r="Z45" s="3">
         <v>3700</v>
       </c>
       <c r="AA45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AB45" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>64400</v>
+      </c>
+      <c r="E46" s="3">
         <v>73500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>83800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>90200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>96000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>17500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>23000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>33000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>38300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>44000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>51900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>60700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>63200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>76100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>128400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>143100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>87300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>98200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>119300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>98400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>76400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>93400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>113100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>125200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>139500</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3407,8 +3511,8 @@
       <c r="J47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3443,31 +3547,34 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X47" s="3">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y47" s="3">
         <v>2000</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>200</v>
+      </c>
+      <c r="E48" s="3">
         <v>100</v>
-      </c>
-      <c r="E48" s="3">
-        <v>200</v>
       </c>
       <c r="F48" s="3">
         <v>200</v>
@@ -3475,8 +3582,8 @@
       <c r="G48" s="3">
         <v>200</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>5</v>
+      <c r="H48" s="3">
+        <v>200</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>5</v>
@@ -3484,59 +3591,62 @@
       <c r="J48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L48" s="3">
+        <v>0</v>
+      </c>
+      <c r="M48" s="3">
         <v>100</v>
-      </c>
-      <c r="M48" s="3">
-        <v>300</v>
       </c>
       <c r="N48" s="3">
         <v>300</v>
       </c>
       <c r="O48" s="3">
+        <v>300</v>
+      </c>
+      <c r="P48" s="3">
         <v>400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5400</v>
-      </c>
-      <c r="V48" s="3">
-        <v>4600</v>
       </c>
       <c r="W48" s="3">
         <v>4600</v>
       </c>
       <c r="X48" s="3">
+        <v>4600</v>
+      </c>
+      <c r="Y48" s="3">
         <v>900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3588,20 +3698,20 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>5</v>
+      <c r="T49" s="3">
+        <v>0</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V49" s="3">
+      <c r="V49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W49" s="3">
         <v>4000</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
-      </c>
-      <c r="X49" s="3" t="s">
-        <v>5</v>
+      <c r="X49" s="3">
+        <v>0</v>
       </c>
       <c r="Y49" s="3" t="s">
         <v>5</v>
@@ -3612,8 +3722,11 @@
       <c r="AA49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,85 +3882,91 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E52" s="3">
         <v>2500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>53500</v>
-      </c>
-      <c r="W52" s="3">
-        <v>200</v>
       </c>
       <c r="X52" s="3">
         <v>200</v>
       </c>
       <c r="Y52" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z52" s="3">
         <v>100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,85 +4042,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>66900</v>
+      </c>
+      <c r="E54" s="3">
         <v>76200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>86600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>91700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>97700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>19300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>25000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>35300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>40800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>46900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>55200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>64300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>67000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>81300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>134000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>149200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>93700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>107700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>130800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>160500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>81200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>96600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>114400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>126300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>139900</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,85 +4184,89 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E57" s="3">
         <v>4000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>10000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>14100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>19400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4150,7 +4283,7 @@
         <v>100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -4177,11 +4310,11 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>33400</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>5</v>
       </c>
@@ -4197,8 +4330,8 @@
       <c r="W58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -4209,162 +4342,171 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E59" s="3">
         <v>1300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2300</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3">
         <v>1900</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L59" s="3">
         <v>7000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>18100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>17000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>18600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>14300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>42500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>16900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>7200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>6800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E60" s="3">
         <v>12700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7500</v>
-      </c>
-      <c r="H60" s="3">
-        <v>6400</v>
       </c>
       <c r="I60" s="3">
         <v>6400</v>
       </c>
       <c r="J60" s="3">
+        <v>6400</v>
+      </c>
+      <c r="K60" s="3">
         <v>7500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9300</v>
-      </c>
-      <c r="L60" s="3">
-        <v>6800</v>
       </c>
       <c r="M60" s="3">
         <v>6800</v>
       </c>
       <c r="N60" s="3">
+        <v>6800</v>
+      </c>
+      <c r="O60" s="3">
         <v>8600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>18400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>21000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>57600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>21500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>21800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>23200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>24200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>56600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>29300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>11900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>10600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4375,13 +4517,13 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
         <v>100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -4411,26 +4553,26 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>33300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>33200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>33000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>32900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>32800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>32700</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4440,8 +4582,11 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4451,8 +4596,8 @@
       <c r="E62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F62" s="3">
-        <v>1300</v>
+      <c r="F62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G62" s="3">
         <v>1300</v>
@@ -4466,8 +4611,8 @@
       <c r="J62" s="3">
         <v>1300</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>5</v>
+      <c r="K62" s="3">
+        <v>1300</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>5</v>
@@ -4478,47 +4623,50 @@
       <c r="N62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
         <v>1400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>300</v>
       </c>
-      <c r="Z62" s="3">
-        <v>0</v>
-      </c>
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,85 +4902,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E66" s="3">
         <v>12700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9300</v>
-      </c>
-      <c r="L66" s="3">
-        <v>6800</v>
       </c>
       <c r="M66" s="3">
         <v>6800</v>
       </c>
       <c r="N66" s="3">
+        <v>6800</v>
+      </c>
+      <c r="O66" s="3">
         <v>8600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>18400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>22400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>59100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>56300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>56200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>58200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>59300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>91000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>63600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>12200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>10600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5035,11 +5202,11 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
         <v>200</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
@@ -5085,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,85 +5332,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-731200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-719100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-707000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-697600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-691300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-685100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-678600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-668500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-662700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-652800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-643300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-634900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-639500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-628000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-606700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-586700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-566200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-543000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-518300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-350900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-310600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-162800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-146000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-129500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-110600</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,85 +5652,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>52100</v>
+      </c>
+      <c r="E76" s="3">
         <v>63500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>74900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>83400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>88700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>17300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>26400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>31200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>40100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>48400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>55700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>48600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>58900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>74900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>92900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>37500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>49500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>71500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>69500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>17600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>87000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>102200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>115600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>130400</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9400</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-6200</v>
       </c>
       <c r="G81" s="3">
         <v>-6200</v>
       </c>
       <c r="H81" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="I81" s="3">
         <v>-6600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-10100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-73300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-21300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-19900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-20600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-23200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-24700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-167400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-40200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-21500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-23200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-15200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,8 +6009,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5826,36 +6024,36 @@
       <c r="F83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H83" s="3">
         <v>-200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
       <c r="J83" s="3">
         <v>0</v>
       </c>
       <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
         <v>-200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
       <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
@@ -5863,7 +6061,7 @@
         <v>0</v>
       </c>
       <c r="S83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T83" s="3">
         <v>100</v>
@@ -5875,10 +6073,10 @@
         <v>100</v>
       </c>
       <c r="W83" s="3">
+        <v>100</v>
+      </c>
+      <c r="X83" s="3">
         <v>-200</v>
-      </c>
-      <c r="X83" s="3">
-        <v>100</v>
       </c>
       <c r="Y83" s="3">
         <v>100</v>
@@ -5887,10 +6085,13 @@
         <v>100</v>
       </c>
       <c r="AA83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,85 +6487,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-8500</v>
+        <v>-9000</v>
       </c>
       <c r="E89" s="3">
         <v>-8500</v>
       </c>
       <c r="F89" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="G89" s="3">
         <v>-8000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-9600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-56400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-17500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-16300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-12600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-25400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-23600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-35900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-52200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-16400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-19300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-12700</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>-16600</v>
       </c>
       <c r="AA89" s="3">
         <v>-16600</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3">
+        <v>-16600</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,13 +6599,14 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>5</v>
+      <c r="D91" s="3">
+        <v>-100</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>5</v>
@@ -6406,8 +6626,8 @@
       <c r="J91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -6416,7 +6636,7 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O91" s="3">
         <v>-100</v>
@@ -6425,7 +6645,7 @@
         <v>-100</v>
       </c>
       <c r="Q91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -6437,11 +6657,11 @@
         <v>0</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
@@ -6457,8 +6677,11 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,85 +6837,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>19000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-62400</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>5000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>16700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1000</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>1000</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>2000</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>21100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>66000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>5500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>15400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>27500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6743,8 +6976,8 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6794,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,13 +7267,16 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
@@ -7040,70 +7285,73 @@
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>82700</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>39800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-33600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>73500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>8000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>53600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-23000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>23000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>3000</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7128,8 +7376,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -7164,11 +7412,11 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X101" s="3">
-        <v>0</v>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y101" s="3">
         <v>0</v>
@@ -7176,84 +7424,90 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-13300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>10500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>15200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>8200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-15600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-51100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-15400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>61000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-15400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-23600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>38900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>13900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-31400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>3100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>12400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-20700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VYNE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VYNE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
   <si>
     <t>VYNE</t>
   </si>
@@ -656,139 +656,143 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>5</v>
+      <c r="D8" s="3">
+        <v>200</v>
       </c>
       <c r="E8" s="3">
         <v>100</v>
       </c>
       <c r="F8" s="3">
+        <v>100</v>
+      </c>
+      <c r="G8" s="3">
         <v>200</v>
-      </c>
-      <c r="G8" s="3">
-        <v>100</v>
       </c>
       <c r="H8" s="3">
         <v>100</v>
@@ -803,44 +807,44 @@
         <v>100</v>
       </c>
       <c r="L8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
         <v>200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1800</v>
       </c>
-      <c r="X8" s="3">
-        <v>0</v>
-      </c>
       <c r="Y8" s="3">
         <v>0</v>
       </c>
@@ -848,13 +852,16 @@
         <v>0</v>
       </c>
       <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="3">
         <v>300</v>
       </c>
-      <c r="AB8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -894,33 +901,33 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3">
         <v>900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>300</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>5</v>
       </c>
@@ -933,22 +940,25 @@
       <c r="AB9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E10" s="3">
         <v>100</v>
       </c>
       <c r="F10" s="3">
+        <v>100</v>
+      </c>
+      <c r="G10" s="3">
         <v>200</v>
-      </c>
-      <c r="G10" s="3">
-        <v>100</v>
       </c>
       <c r="H10" s="3">
         <v>100</v>
@@ -962,8 +972,8 @@
       <c r="K10" s="3">
         <v>100</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
+      <c r="L10" s="3">
+        <v>100</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
@@ -974,33 +984,33 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="3">
-        <v>0</v>
+      <c r="P10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q10" s="3">
+        <v>0</v>
+      </c>
+      <c r="R10" s="3">
         <v>3100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>11500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1500</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1013,8 +1023,11 @@
       <c r="AB10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1043,88 +1056,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E12" s="3">
         <v>9700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>10200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>7300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>19500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>5000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>4300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>6600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>13100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>16000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>11800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>12500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>12600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>10800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,8 +1220,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1232,8 +1252,8 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1283,8 +1303,11 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1363,8 +1386,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1416,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E17" s="3">
         <v>12900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>39800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>21900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>10000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>26300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>26800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>178900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>41600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>21900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>23200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>19400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>16200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-12800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-13100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-7400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-6800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-6200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-10300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-8700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-38900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-17800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-9500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-9800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-22000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-23500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-167200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-39800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-21900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-23200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-19400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-15900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-18400</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,13 +1613,14 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
+      <c r="D20" s="3">
+        <v>-600</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>5</v>
@@ -1609,44 +1643,44 @@
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>700</v>
-      </c>
-      <c r="X20" s="3">
-        <v>400</v>
       </c>
       <c r="Y20" s="3">
         <v>400</v>
@@ -1655,93 +1689,99 @@
         <v>400</v>
       </c>
       <c r="AA20" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB20" s="3">
         <v>500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-12800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-13100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-10400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-7400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-6800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-6200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-10300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-7900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-9100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-8200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-8700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-38900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-17800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-9600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-9800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-21900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-23600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-166500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-39100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-21700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-22700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-18900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-15300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1769,8 +1809,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1782,22 +1822,22 @@
         <v>0</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>5600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3500</v>
-      </c>
-      <c r="R22" s="3">
-        <v>1100</v>
       </c>
       <c r="S22" s="3">
         <v>1100</v>
       </c>
       <c r="T22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U22" s="3">
         <v>1200</v>
-      </c>
-      <c r="U22" s="3">
-        <v>1100</v>
       </c>
       <c r="V22" s="3">
         <v>1100</v>
@@ -1805,111 +1845,117 @@
       <c r="W22" s="3">
         <v>1100</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y22" s="3">
+      <c r="X22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z22" s="3">
         <v>300</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-12000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-12200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9400</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-6200</v>
       </c>
       <c r="H23" s="3">
         <v>-6200</v>
       </c>
       <c r="I23" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="J23" s="3">
         <v>-6100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-8200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-8700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-44700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-21300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-10700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-10900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-23200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-24700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-167700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-40200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-21500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-23200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-15400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>5</v>
+      <c r="D24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>5</v>
@@ -1929,8 +1975,8 @@
       <c r="K24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1942,11 +1988,11 @@
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-400</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
@@ -1960,28 +2006,31 @@
         <v>0</v>
       </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>-300</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-      <c r="X24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>0</v>
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
       </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>-200</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9400</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-6200</v>
       </c>
       <c r="H26" s="3">
         <v>-6200</v>
       </c>
       <c r="I26" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="J26" s="3">
         <v>-6100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-8200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-8700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-44200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-21300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-10700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-10900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-23200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-24700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-167400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-40200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-21500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-23200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-15200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-8200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-8700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-44200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-21300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-10700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-10900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-23200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-24700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-167400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-40200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-21500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-23200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-15200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2321,43 +2382,43 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-500</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-2200</v>
-      </c>
-      <c r="M29" s="3">
-        <v>-200</v>
       </c>
       <c r="N29" s="3">
         <v>-200</v>
       </c>
       <c r="O29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P29" s="3">
         <v>13400</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-29100</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R29" s="3">
+      <c r="R29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S29" s="3">
         <v>-9200</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-9700</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -2371,8 +2432,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
@@ -2380,8 +2441,11 @@
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,13 +2607,16 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
+      <c r="D32" s="3">
+        <v>600</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>5</v>
@@ -2569,44 +2639,44 @@
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-700</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-400</v>
       </c>
       <c r="Y32" s="3">
         <v>-400</v>
@@ -2615,93 +2685,99 @@
         <v>-400</v>
       </c>
       <c r="AA32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9400</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-6200</v>
       </c>
       <c r="H33" s="3">
         <v>-6200</v>
       </c>
       <c r="I33" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="J33" s="3">
         <v>-6600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-10100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-8500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-73300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-21300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-19900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-20600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-23200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-24700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-167400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-40200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-21500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-23200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-15200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9400</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-6200</v>
       </c>
       <c r="H35" s="3">
         <v>-6200</v>
       </c>
       <c r="I35" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="J35" s="3">
         <v>-6600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-10100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-8500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-73300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-21300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-19900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-20600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-23200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-24700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-167400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-40200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-21500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-23200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-15200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,109 +3091,113 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>28200</v>
+      </c>
+      <c r="E41" s="3">
         <v>19900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>16300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>29600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>19100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>30600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>15400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>20600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>30200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>30900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>35500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>42800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>50500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>42300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>52300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>103400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>118500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>57600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>73000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>96500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>57600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>43800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>34200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>65100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>62000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>49500</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E42" s="3">
         <v>41600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>53900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>48500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>66900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>62600</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -3151,22 +3241,25 @@
         <v>0</v>
       </c>
       <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
         <v>12100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>57100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>44400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>59600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3185,68 +3278,71 @@
       <c r="H43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>10900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>10800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>15800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>11200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>10400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>8300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>100</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3274,8 +3370,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3283,39 +3379,39 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P44" s="3">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q44" s="3">
         <v>7300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>8100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>8300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>8100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>7400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>6700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1400</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z44" s="3" t="s">
         <v>5</v>
       </c>
@@ -3325,8 +3421,11 @@
       <c r="AB44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3354,139 +3453,145 @@
       <c r="K45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M45" s="3">
         <v>2200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>6600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>29300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>19100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2100</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>3700</v>
       </c>
       <c r="AA45" s="3">
         <v>3700</v>
       </c>
       <c r="AB45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AC45" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>54900</v>
+      </c>
+      <c r="E46" s="3">
         <v>64400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>73500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>83800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>90200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>96000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>17500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>23000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>33000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>38300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>44000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>51900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>60700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>63200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>76100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>128400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>143100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>87300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>98200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>119300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>98400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>76400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>93400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>113100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>125200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>139500</v>
       </c>
     </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3514,8 +3619,8 @@
       <c r="K47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3550,23 +3655,26 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y47" s="3">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z47" s="3">
         <v>2000</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3574,10 +3682,10 @@
         <v>200</v>
       </c>
       <c r="E48" s="3">
+        <v>200</v>
+      </c>
+      <c r="F48" s="3">
         <v>100</v>
-      </c>
-      <c r="F48" s="3">
-        <v>200</v>
       </c>
       <c r="G48" s="3">
         <v>200</v>
@@ -3585,8 +3693,8 @@
       <c r="H48" s="3">
         <v>200</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>5</v>
+      <c r="I48" s="3">
+        <v>200</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
@@ -3594,59 +3702,62 @@
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M48" s="3">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3">
         <v>100</v>
-      </c>
-      <c r="N48" s="3">
-        <v>300</v>
       </c>
       <c r="O48" s="3">
         <v>300</v>
       </c>
       <c r="P48" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q48" s="3">
         <v>400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5400</v>
-      </c>
-      <c r="W48" s="3">
-        <v>4600</v>
       </c>
       <c r="X48" s="3">
         <v>4600</v>
       </c>
       <c r="Y48" s="3">
+        <v>4600</v>
+      </c>
+      <c r="Z48" s="3">
         <v>900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3701,20 +3812,20 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>5</v>
+      <c r="U49" s="3">
+        <v>0</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W49" s="3">
+      <c r="W49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X49" s="3">
         <v>4000</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y49" s="3" t="s">
-        <v>5</v>
+      <c r="Y49" s="3">
+        <v>0</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>5</v>
@@ -3725,8 +3836,11 @@
       <c r="AB49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,88 +4002,94 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E52" s="3">
         <v>2300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>53500</v>
-      </c>
-      <c r="X52" s="3">
-        <v>200</v>
       </c>
       <c r="Y52" s="3">
         <v>200</v>
       </c>
       <c r="Z52" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA52" s="3">
         <v>100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,88 +4168,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>56400</v>
+      </c>
+      <c r="E54" s="3">
         <v>66900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>76200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>86600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>91700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>97700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>19300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>25000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>35300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>40800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>46900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>55200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>64300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>67000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>81300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>134000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>149200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>93700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>107700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>130800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>160500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>81200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>96600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>114400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>126300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>139900</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,88 +4315,92 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E57" s="3">
         <v>2700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>10000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>14100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>19400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4286,7 +4420,7 @@
         <v>100</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -4313,11 +4447,11 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>33400</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>5</v>
       </c>
@@ -4333,8 +4467,8 @@
       <c r="X58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -4345,168 +4479,177 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E59" s="3">
         <v>3400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2300</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K59" s="3">
         <v>1900</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M59" s="3">
         <v>7000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>14200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>18100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>17000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>18600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>14300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>42500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>16900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>7200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>6800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E60" s="3">
         <v>14800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7500</v>
-      </c>
-      <c r="I60" s="3">
-        <v>6400</v>
       </c>
       <c r="J60" s="3">
         <v>6400</v>
       </c>
       <c r="K60" s="3">
+        <v>6400</v>
+      </c>
+      <c r="L60" s="3">
         <v>7500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9300</v>
-      </c>
-      <c r="M60" s="3">
-        <v>6800</v>
       </c>
       <c r="N60" s="3">
         <v>6800</v>
       </c>
       <c r="O60" s="3">
+        <v>6800</v>
+      </c>
+      <c r="P60" s="3">
         <v>8600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>18400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>21000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>57600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>21500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>21800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>23200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>24200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>56600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>29300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>11900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>10600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4520,13 +4663,13 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>100</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -4556,26 +4699,26 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>33300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>33200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>33000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>32900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>32800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>32700</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -4585,8 +4728,11 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4599,8 +4745,8 @@
       <c r="F62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G62" s="3">
-        <v>1300</v>
+      <c r="G62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H62" s="3">
         <v>1300</v>
@@ -4614,8 +4760,8 @@
       <c r="K62" s="3">
         <v>1300</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>5</v>
+      <c r="L62" s="3">
+        <v>1300</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>5</v>
@@ -4626,47 +4772,50 @@
       <c r="O62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="P62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3">
         <v>1400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>300</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
-      </c>
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,88 +5060,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E66" s="3">
         <v>14800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9300</v>
-      </c>
-      <c r="M66" s="3">
-        <v>6800</v>
       </c>
       <c r="N66" s="3">
         <v>6800</v>
       </c>
       <c r="O66" s="3">
+        <v>6800</v>
+      </c>
+      <c r="P66" s="3">
         <v>8600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>18400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>22400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>59100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>56300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>56200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>58200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>59300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>91000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>63600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>12200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>10600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5205,11 +5373,11 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
         <v>200</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
       <c r="N70" s="3">
         <v>0</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,88 +5506,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-739800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-731200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-719100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-707000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-697600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-691300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-685100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-678600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-668500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-662700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-652800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-643300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-634900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-639500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-628000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-606700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-586700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-566200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-543000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-518300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-350900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-310600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-162800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-146000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-129500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-110600</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,88 +5838,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>44100</v>
+      </c>
+      <c r="E76" s="3">
         <v>52100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>63500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>74900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>83400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>88700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>17300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>26400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>31200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>40100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>48400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>55700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>48600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>58900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>74900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>92900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>37500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>49500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>71500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>69500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>87000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>102200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>115600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>130400</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9400</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-6200</v>
       </c>
       <c r="H81" s="3">
         <v>-6200</v>
       </c>
       <c r="I81" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="J81" s="3">
         <v>-6600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-10100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-8500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-73300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-21300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-19900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-20600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-23200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-24700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-167400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-40200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-21500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-23200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-15200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,8 +6208,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6027,36 +6226,36 @@
       <c r="G83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I83" s="3">
         <v>-200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>200</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
       <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
         <v>-200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>200</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
       <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
         <v>100</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
@@ -6064,7 +6263,7 @@
         <v>0</v>
       </c>
       <c r="T83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U83" s="3">
         <v>100</v>
@@ -6076,10 +6275,10 @@
         <v>100</v>
       </c>
       <c r="X83" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y83" s="3">
         <v>-200</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>100</v>
       </c>
       <c r="Z83" s="3">
         <v>100</v>
@@ -6088,10 +6287,13 @@
         <v>100</v>
       </c>
       <c r="AB83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,88 +6704,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3">
         <v>-9000</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-8500</v>
       </c>
       <c r="F89" s="3">
         <v>-8500</v>
       </c>
       <c r="G89" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="H89" s="3">
         <v>-8000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-9600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-9000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-56400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-17500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-16300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-12600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-25400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-23600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-35900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-52200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-16400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-19300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-12700</v>
-      </c>
-      <c r="AA89" s="3">
-        <v>-16600</v>
       </c>
       <c r="AB89" s="3">
         <v>-16600</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3">
+        <v>-16600</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,17 +6820,18 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F91" s="3" t="s">
         <v>5</v>
       </c>
@@ -6629,8 +6850,8 @@
       <c r="K91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -6639,7 +6860,7 @@
         <v>0</v>
       </c>
       <c r="O91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P91" s="3">
         <v>-100</v>
@@ -6648,7 +6869,7 @@
         <v>-100</v>
       </c>
       <c r="R91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -6660,11 +6881,11 @@
         <v>0</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
@@ -6680,8 +6901,11 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,88 +7067,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3">
         <v>12700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>19000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-62400</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>5000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>16700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1000</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>1000</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>2000</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>21100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>66000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>5500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>15400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>27500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7183,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6979,8 +7213,8 @@
       <c r="K96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7030,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,17 +7513,20 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
@@ -7288,70 +7534,73 @@
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>82700</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>39800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-33600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>73500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>8000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>53600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-23000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>23000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>3000</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7379,8 +7628,8 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7415,11 +7664,11 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>0</v>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
@@ -7427,87 +7676,93 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>3600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-13300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>15200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-9600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>8200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-51100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-15400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>61000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-15400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-23600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>38900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>13900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-31400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>3100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>12400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-20700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VYNE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VYNE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="92">
   <si>
     <t>VYNE</t>
   </si>
@@ -656,146 +656,150 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3">
         <v>200</v>
-      </c>
-      <c r="E8" s="3">
-        <v>100</v>
       </c>
       <c r="F8" s="3">
         <v>100</v>
       </c>
       <c r="G8" s="3">
+        <v>100</v>
+      </c>
+      <c r="H8" s="3">
         <v>200</v>
-      </c>
-      <c r="H8" s="3">
-        <v>100</v>
       </c>
       <c r="I8" s="3">
         <v>100</v>
@@ -810,44 +814,44 @@
         <v>100</v>
       </c>
       <c r="M8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
         <v>200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1800</v>
       </c>
-      <c r="Y8" s="3">
-        <v>0</v>
-      </c>
       <c r="Z8" s="3">
         <v>0</v>
       </c>
@@ -855,13 +859,16 @@
         <v>0</v>
       </c>
       <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
         <v>300</v>
       </c>
-      <c r="AC8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -904,33 +911,33 @@
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3">
         <v>900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>300</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>5</v>
       </c>
@@ -943,25 +950,28 @@
       <c r="AC9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>100</v>
+      </c>
+      <c r="E10" s="3">
         <v>200</v>
-      </c>
-      <c r="E10" s="3">
-        <v>100</v>
       </c>
       <c r="F10" s="3">
         <v>100</v>
       </c>
       <c r="G10" s="3">
+        <v>100</v>
+      </c>
+      <c r="H10" s="3">
         <v>200</v>
-      </c>
-      <c r="H10" s="3">
-        <v>100</v>
       </c>
       <c r="I10" s="3">
         <v>100</v>
@@ -975,8 +985,8 @@
       <c r="L10" s="3">
         <v>100</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
+      <c r="M10" s="3">
+        <v>100</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
@@ -987,33 +997,33 @@
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q10" s="3">
-        <v>0</v>
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R10" s="3">
+        <v>0</v>
+      </c>
+      <c r="S10" s="3">
         <v>3100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>11500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1500</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1026,8 +1036,11 @@
       <c r="AC10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,91 +1070,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E12" s="3">
         <v>6100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>9700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>10200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>4500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>19500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>5000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>4300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>6600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>13100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>16000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>11800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>12500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>12600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>10800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,8 +1240,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1255,8 +1275,8 @@
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1306,8 +1326,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1443,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E17" s="3">
         <v>9400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>12900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>39800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>21900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>26300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>26800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>178900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>41600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>21900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>23200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>19400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>16200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-9200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-12800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-10400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-7400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-6800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-9300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-8300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-38900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-17800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-9500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-9800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-22000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-23500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-167200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-39800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-21900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-23200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-19400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-15900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-18400</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,13 +1647,14 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-600</v>
+        <v>-1800</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>5</v>
@@ -1631,8 +1665,8 @@
       <c r="G20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>5</v>
+      <c r="H20" s="3">
+        <v>-1000</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>5</v>
@@ -1646,44 +1680,44 @@
       <c r="L20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>700</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>400</v>
       </c>
       <c r="Z20" s="3">
         <v>400</v>
@@ -1692,96 +1726,102 @@
         <v>400</v>
       </c>
       <c r="AB20" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC20" s="3">
         <v>500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-8600</v>
+        <v>-5700</v>
       </c>
       <c r="E21" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-12800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-13100</v>
       </c>
-      <c r="G21" s="3">
-        <v>-10400</v>
-      </c>
       <c r="H21" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="I21" s="3">
         <v>-7400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-6800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-10300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-7900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-9100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-8200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-38900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-17800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-9600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-9800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-21900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-23600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-166500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-39100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-21700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-22700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-18900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-15300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1812,8 +1852,8 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1825,22 +1865,22 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>5600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3500</v>
-      </c>
-      <c r="S22" s="3">
-        <v>1100</v>
       </c>
       <c r="T22" s="3">
         <v>1100</v>
       </c>
       <c r="U22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V22" s="3">
         <v>1200</v>
-      </c>
-      <c r="V22" s="3">
-        <v>1100</v>
       </c>
       <c r="W22" s="3">
         <v>1100</v>
@@ -1848,117 +1888,123 @@
       <c r="X22" s="3">
         <v>1100</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z22" s="3">
+      <c r="Y22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Z22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA22" s="3">
         <v>300</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
-      </c>
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-12000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-12200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9400</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-6200</v>
       </c>
       <c r="I23" s="3">
         <v>-6200</v>
       </c>
       <c r="J23" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="K23" s="3">
         <v>-6100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-10000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-8200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-44700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-21300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-10700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-10900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-23200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-24700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-167700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-40200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-21500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-23200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-19000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-15400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>5</v>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>5</v>
@@ -1978,8 +2024,8 @@
       <c r="L24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1991,11 +2037,11 @@
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>-400</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
@@ -2009,28 +2055,31 @@
         <v>0</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>-300</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>0</v>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA24" s="3">
         <v>0</v>
       </c>
       <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>-200</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2161,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9400</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-6200</v>
       </c>
       <c r="I26" s="3">
         <v>-6200</v>
       </c>
       <c r="J26" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="K26" s="3">
         <v>-6100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-8200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-44200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-21300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-10700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-10900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-23200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-24700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-167400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-40200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-21500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-23200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-19000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-15200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-8200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-44200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-21300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-10700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-10900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-23200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-24700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-167400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-40200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-21500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-23200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-19000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-15200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2385,43 +2446,43 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-500</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-2200</v>
-      </c>
-      <c r="N29" s="3">
-        <v>-200</v>
       </c>
       <c r="O29" s="3">
         <v>-200</v>
       </c>
       <c r="P29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q29" s="3">
         <v>13400</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-29100</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T29" s="3">
         <v>-9200</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-9700</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="V29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2435,8 +2496,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,13 +2677,16 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>600</v>
+        <v>1800</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>5</v>
@@ -2627,8 +2697,8 @@
       <c r="G32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>5</v>
+      <c r="H32" s="3">
+        <v>1000</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>5</v>
@@ -2642,44 +2712,44 @@
       <c r="L32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-700</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-400</v>
       </c>
       <c r="Z32" s="3">
         <v>-400</v>
@@ -2688,96 +2758,102 @@
         <v>-400</v>
       </c>
       <c r="AB32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9400</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-6200</v>
       </c>
       <c r="I33" s="3">
         <v>-6200</v>
       </c>
       <c r="J33" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="K33" s="3">
         <v>-6600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-8500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-73300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-21300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-19900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-20600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-23200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-24700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-167400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-40200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-21500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-23200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-19000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-15200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2935,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9400</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-6200</v>
       </c>
       <c r="I35" s="3">
         <v>-6200</v>
       </c>
       <c r="J35" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="K35" s="3">
         <v>-6600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-8500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-73300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-21300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-19900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-20600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-23200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-24700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-167400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-40200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-21500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-23200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-19000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-15200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,115 +3178,119 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E41" s="3">
         <v>28200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>19900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>16300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>29600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>19100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>30600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>15400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>20600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>30200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>30900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>35500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>42800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>50500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>42300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>52300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>103400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>118500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>57600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>73000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>96500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>57600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>43800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>34200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>65100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>62000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>49500</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E42" s="3">
         <v>22100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>41600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>53900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>48500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>66900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>62600</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -3244,22 +3334,25 @@
         <v>0</v>
       </c>
       <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
         <v>12100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>57100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>44400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>59600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3281,68 +3374,71 @@
       <c r="I43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K43" s="3">
         <v>300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>10100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>10900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>10800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>15800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>11200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>10400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>8300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>100</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3373,8 +3469,8 @@
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3382,39 +3478,39 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q44" s="3">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R44" s="3">
         <v>7300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>8100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>8300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>8100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>7400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>6700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1400</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA44" s="3" t="s">
         <v>5</v>
       </c>
@@ -3424,8 +3520,11 @@
       <c r="AC44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3456,142 +3555,148 @@
       <c r="L45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N45" s="3">
         <v>2200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>29300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>19100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2100</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>3700</v>
       </c>
       <c r="AB45" s="3">
         <v>3700</v>
       </c>
       <c r="AC45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AD45" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>44300</v>
+      </c>
+      <c r="E46" s="3">
         <v>54900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>64400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>73500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>83800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>90200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>96000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>17500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>23000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>33000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>38300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>44000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>51900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>60700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>63200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>76100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>128400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>143100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>87300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>98200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>119300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>98400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>76400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>93400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>113100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>125200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>139500</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3622,8 +3727,8 @@
       <c r="L47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3658,37 +3763,40 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z47" s="3">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA47" s="3">
         <v>2000</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E48" s="3">
         <v>200</v>
       </c>
       <c r="F48" s="3">
+        <v>200</v>
+      </c>
+      <c r="G48" s="3">
         <v>100</v>
-      </c>
-      <c r="G48" s="3">
-        <v>200</v>
       </c>
       <c r="H48" s="3">
         <v>200</v>
@@ -3696,8 +3804,8 @@
       <c r="I48" s="3">
         <v>200</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
+      <c r="J48" s="3">
+        <v>200</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
@@ -3705,59 +3813,62 @@
       <c r="L48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N48" s="3">
+        <v>0</v>
+      </c>
+      <c r="O48" s="3">
         <v>100</v>
-      </c>
-      <c r="O48" s="3">
-        <v>300</v>
       </c>
       <c r="P48" s="3">
         <v>300</v>
       </c>
       <c r="Q48" s="3">
+        <v>300</v>
+      </c>
+      <c r="R48" s="3">
         <v>400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5400</v>
-      </c>
-      <c r="X48" s="3">
-        <v>4600</v>
       </c>
       <c r="Y48" s="3">
         <v>4600</v>
       </c>
       <c r="Z48" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AA48" s="3">
         <v>900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3815,20 +3926,20 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>5</v>
+      <c r="V49" s="3">
+        <v>0</v>
       </c>
       <c r="W49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X49" s="3">
+      <c r="X49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y49" s="3">
         <v>4000</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z49" s="3" t="s">
-        <v>5</v>
+      <c r="Z49" s="3">
+        <v>0</v>
       </c>
       <c r="AA49" s="3" t="s">
         <v>5</v>
@@ -3839,8 +3950,11 @@
       <c r="AC49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,91 +4122,97 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>200</v>
+      </c>
+      <c r="E52" s="3">
         <v>1300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>53500</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>200</v>
       </c>
       <c r="Z52" s="3">
         <v>200</v>
       </c>
       <c r="AA52" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB52" s="3">
         <v>100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,91 +4294,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>44700</v>
+      </c>
+      <c r="E54" s="3">
         <v>56400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>66900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>76200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>86600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>91700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>97700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>19300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>25000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>35300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>40800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>46900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>55200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>64300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>67000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>81300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>134000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>149200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>93700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>107700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>130800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>160500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>81200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>96600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>114400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>126300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>139900</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,96 +4446,100 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E57" s="3">
         <v>3500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>14100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>19400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
         <v>100</v>
@@ -4423,7 +4557,7 @@
         <v>100</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4450,11 +4584,11 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>33400</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>5</v>
       </c>
@@ -4470,8 +4604,8 @@
       <c r="Y58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="Z58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
@@ -4482,174 +4616,183 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>1300</v>
+      <c r="D59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E59" s="3">
         <v>3400</v>
       </c>
       <c r="F59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="G59" s="3">
         <v>1300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2300</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L59" s="3">
         <v>1900</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N59" s="3">
         <v>7000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>14200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>18100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>17000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>18600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>14300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>42500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>16900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>6500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>7200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>6800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E60" s="3">
         <v>12300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>14800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7500</v>
-      </c>
-      <c r="J60" s="3">
-        <v>6400</v>
       </c>
       <c r="K60" s="3">
         <v>6400</v>
       </c>
       <c r="L60" s="3">
+        <v>6400</v>
+      </c>
+      <c r="M60" s="3">
         <v>7500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9300</v>
-      </c>
-      <c r="N60" s="3">
-        <v>6800</v>
       </c>
       <c r="O60" s="3">
         <v>6800</v>
       </c>
       <c r="P60" s="3">
+        <v>6800</v>
+      </c>
+      <c r="Q60" s="3">
         <v>8600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>18400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>21000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>57600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>21500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>21800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>23200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>24200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>56600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>29300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>11900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>10600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4666,13 +4809,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
         <v>100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4702,26 +4845,26 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>33300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>33200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>33000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>32900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>32800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>32700</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -4731,8 +4874,11 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4748,8 +4894,8 @@
       <c r="G62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H62" s="3">
-        <v>1300</v>
+      <c r="H62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I62" s="3">
         <v>1300</v>
@@ -4763,8 +4909,8 @@
       <c r="L62" s="3">
         <v>1300</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>5</v>
+      <c r="M62" s="3">
+        <v>1300</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>5</v>
@@ -4775,47 +4921,50 @@
       <c r="P62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
         <v>1400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>300</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
-      </c>
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,91 +5218,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E66" s="3">
         <v>12300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>8800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9300</v>
-      </c>
-      <c r="N66" s="3">
-        <v>6800</v>
       </c>
       <c r="O66" s="3">
         <v>6800</v>
       </c>
       <c r="P66" s="3">
+        <v>6800</v>
+      </c>
+      <c r="Q66" s="3">
         <v>8600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>22400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>59100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>56300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>56200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>58200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>59300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>91000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>63600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>12200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>10600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5376,11 +5544,11 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>200</v>
       </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,91 +5680,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-745500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-739800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-731200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-719100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-707000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-697600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-691300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-685100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-678600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-668500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-662700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-652800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-643300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-634900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-639500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-628000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-606700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-586700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-566200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-543000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-518300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-350900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-310600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-162800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-146000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-129500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-110600</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,91 +6024,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E76" s="3">
         <v>44100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>52100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>63500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>74900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>83400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>88700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>17300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>26400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>31200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>40100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>48400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>55700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>48600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>58900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>74900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>92900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>37500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>49500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>71500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>69500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>17600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>87000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>102200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>115600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>130400</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6196,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9400</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-6200</v>
       </c>
       <c r="I81" s="3">
         <v>-6200</v>
       </c>
       <c r="J81" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="K81" s="3">
         <v>-6600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-8500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-73300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-21300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-19900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-20600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-23200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-24700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-167400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-40200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-21500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-23200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-19000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-15200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,8 +6407,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6229,36 +6428,36 @@
       <c r="H83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3">
         <v>-200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>200</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
       <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
         <v>-200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>200</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
       <c r="P83" s="3">
         <v>0</v>
       </c>
       <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
         <v>100</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
@@ -6266,7 +6465,7 @@
         <v>0</v>
       </c>
       <c r="U83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V83" s="3">
         <v>100</v>
@@ -6278,10 +6477,10 @@
         <v>100</v>
       </c>
       <c r="Y83" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z83" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>100</v>
       </c>
       <c r="AA83" s="3">
         <v>100</v>
@@ -6290,10 +6489,13 @@
         <v>100</v>
       </c>
       <c r="AC83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +6921,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
+      <c r="D89" s="3">
+        <v>-10800</v>
       </c>
       <c r="E89" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-9000</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-8500</v>
       </c>
       <c r="G89" s="3">
         <v>-8500</v>
       </c>
       <c r="H89" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="I89" s="3">
         <v>-8000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-9600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-9200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-56400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-17500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-16300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-12600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-25400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-23600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-35900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-52200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-16400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-19300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-12700</v>
-      </c>
-      <c r="AB89" s="3">
-        <v>-16600</v>
       </c>
       <c r="AC89" s="3">
         <v>-16600</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3">
+        <v>-16600</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,20 +7041,21 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E91" s="3">
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G91" s="3" t="s">
         <v>5</v>
       </c>
@@ -6853,8 +7074,8 @@
       <c r="L91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -6863,7 +7084,7 @@
         <v>0</v>
       </c>
       <c r="P91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q91" s="3">
         <v>-100</v>
@@ -6872,7 +7093,7 @@
         <v>-100</v>
       </c>
       <c r="S91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
@@ -6884,11 +7105,11 @@
         <v>0</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3">
         <v>0</v>
       </c>
@@ -6904,8 +7125,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,91 +7297,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
+      <c r="D94" s="3">
+        <v>4700</v>
       </c>
       <c r="E94" s="3">
+        <v>19800</v>
+      </c>
+      <c r="F94" s="3">
         <v>12700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>19000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-62400</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>5000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>16700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>1000</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>1000</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>2000</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>21100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>66000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>5500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>15400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>27500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7216,8 +7450,8 @@
       <c r="L96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,19 +7759,22 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>5</v>
+      <c r="D100" s="3">
+        <v>0</v>
       </c>
       <c r="E100" s="3">
         <v>-100</v>
       </c>
       <c r="F100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G100" s="3">
         <v>0</v>
@@ -7537,70 +7783,73 @@
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>82700</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>39800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-33600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>73500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>8000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>53600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-23000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>23000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>3000</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7631,8 +7880,8 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -7667,11 +7916,11 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>0</v>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA101" s="3">
         <v>0</v>
@@ -7679,90 +7928,96 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-6200</v>
       </c>
       <c r="E102" s="3">
+        <v>8300</v>
+      </c>
+      <c r="F102" s="3">
         <v>3600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-13300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>10500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-11600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>15200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-9600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-8300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>8200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-15600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-51100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-15400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>61000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-15400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-23600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>38900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>13900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-31400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>12400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-20700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VYNE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VYNE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
   <si>
     <t>VYNE</t>
   </si>
@@ -656,160 +656,163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>100</v>
+      </c>
+      <c r="E8" s="3">
         <v>200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>200</v>
-      </c>
-      <c r="G8" s="3">
-        <v>100</v>
       </c>
       <c r="H8" s="3">
         <v>100</v>
       </c>
       <c r="I8" s="3">
+        <v>100</v>
+      </c>
+      <c r="J8" s="3">
         <v>200</v>
-      </c>
-      <c r="J8" s="3">
-        <v>100</v>
       </c>
       <c r="K8" s="3">
         <v>100</v>
@@ -824,44 +827,44 @@
         <v>100</v>
       </c>
       <c r="O8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
         <v>200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1800</v>
       </c>
-      <c r="AA8" s="3">
-        <v>0</v>
-      </c>
       <c r="AB8" s="3">
         <v>0</v>
       </c>
@@ -869,13 +872,16 @@
         <v>0</v>
       </c>
       <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3">
         <v>300</v>
       </c>
-      <c r="AE8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -924,33 +930,33 @@
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S9" s="3">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3">
         <v>900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>300</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB9" s="3" t="s">
         <v>5</v>
       </c>
@@ -963,31 +969,34 @@
       <c r="AE9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>100</v>
+      </c>
+      <c r="E10" s="3">
         <v>200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>200</v>
-      </c>
-      <c r="G10" s="3">
-        <v>100</v>
       </c>
       <c r="H10" s="3">
         <v>100</v>
       </c>
       <c r="I10" s="3">
+        <v>100</v>
+      </c>
+      <c r="J10" s="3">
         <v>200</v>
-      </c>
-      <c r="J10" s="3">
-        <v>100</v>
       </c>
       <c r="K10" s="3">
         <v>100</v>
@@ -1001,8 +1010,8 @@
       <c r="N10" s="3">
         <v>100</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
+      <c r="O10" s="3">
+        <v>100</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
@@ -1013,33 +1022,33 @@
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S10" s="3">
-        <v>0</v>
+      <c r="S10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T10" s="3">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3">
         <v>3100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>11500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1500</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1052,8 +1061,11 @@
       <c r="AE10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1085,97 +1097,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E12" s="3">
         <v>5300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>9700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>10200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>7200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>4100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>4500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>19500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>5000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>4300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>7800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>6600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>13100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>16000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>11800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>12500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>12600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>10800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1263,20 +1279,23 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>-1300</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1301,8 +1320,8 @@
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1352,8 +1371,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1441,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E17" s="3">
         <v>8000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>10600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>39800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>21900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>26300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>26800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>178900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>41600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>21900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>23200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>19400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>16200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-7500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-9200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-12800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-13100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-10400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-10300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-8000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-8300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-8700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-38900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-17800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-9500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-9800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-22000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-23500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-167200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-39800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-21900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-23200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-19400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-15900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-18400</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1682,32 +1714,33 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-500</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H20" s="3">
+        <v>3100</v>
+      </c>
+      <c r="I20" s="3">
         <v>-900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1000</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1720,44 +1753,44 @@
       <c r="N20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>700</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>400</v>
       </c>
       <c r="AB20" s="3">
         <v>400</v>
@@ -1766,102 +1799,108 @@
         <v>400</v>
       </c>
       <c r="AD20" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE20" s="3">
         <v>500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-7400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-7000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-9200</v>
       </c>
-      <c r="G21" s="3">
-        <v>-12800</v>
-      </c>
       <c r="H21" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="I21" s="3">
         <v>-12200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-9400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-7400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-10300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-7900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-8200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-8700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-38900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-17800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-9600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-9800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-21900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-23600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-166500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-39100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-21700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-22700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-18900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-15300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1898,8 +1937,8 @@
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1911,22 +1950,22 @@
         <v>0</v>
       </c>
       <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>5600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>3500</v>
-      </c>
-      <c r="U22" s="3">
-        <v>1100</v>
       </c>
       <c r="V22" s="3">
         <v>1100</v>
       </c>
       <c r="W22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X22" s="3">
         <v>1200</v>
-      </c>
-      <c r="X22" s="3">
-        <v>1100</v>
       </c>
       <c r="Y22" s="3">
         <v>1100</v>
@@ -1934,117 +1973,123 @@
       <c r="Z22" s="3">
         <v>1100</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB22" s="3">
+      <c r="AA22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC22" s="3">
         <v>300</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
-      </c>
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-12000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-12200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9400</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-6200</v>
       </c>
       <c r="K23" s="3">
         <v>-6200</v>
       </c>
       <c r="L23" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="M23" s="3">
         <v>-6100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-10000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-8200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-8700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-44700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-21300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-10700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-10900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-23200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-24700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-167700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-40200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-21500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-23200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-15400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>5</v>
+      <c r="D24" s="3">
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>5</v>
@@ -2052,11 +2097,11 @@
       <c r="F24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>5</v>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>5</v>
@@ -2076,8 +2121,8 @@
       <c r="N24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -2089,11 +2134,11 @@
         <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>-400</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
@@ -2107,28 +2152,31 @@
         <v>0</v>
       </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-300</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>0</v>
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC24" s="3">
         <v>0</v>
       </c>
       <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
         <v>-200</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-12000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-12200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9400</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-6200</v>
       </c>
       <c r="K26" s="3">
         <v>-6200</v>
       </c>
       <c r="L26" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="M26" s="3">
         <v>-6100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-10000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-8200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-8700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-44200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-21300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-10700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-10900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-23200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-24700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-167400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-40200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-21500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-23200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-15200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-7300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-12000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-12200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-10100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-44200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-21300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-10700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-10900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-23200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-24700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-167400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-40200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-21500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-23200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-15200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2492,7 +2552,7 @@
         <v>100</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -2513,43 +2573,43 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-500</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-2200</v>
-      </c>
-      <c r="P29" s="3">
-        <v>-200</v>
       </c>
       <c r="Q29" s="3">
         <v>-200</v>
       </c>
       <c r="R29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S29" s="3">
         <v>13400</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-29100</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V29" s="3">
         <v>-9200</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-9700</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="X29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y29" s="3">
         <v>0</v>
@@ -2563,8 +2623,8 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
@@ -2572,8 +2632,11 @@
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,32 +2816,35 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E32" s="3">
         <v>400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>500</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G32" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H32" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="I32" s="3">
         <v>900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1000</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
@@ -2788,44 +2857,44 @@
       <c r="N32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-700</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-400</v>
       </c>
       <c r="AB32" s="3">
         <v>-400</v>
@@ -2834,102 +2903,108 @@
         <v>-400</v>
       </c>
       <c r="AD32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-12000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-12200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9400</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-6200</v>
       </c>
       <c r="K33" s="3">
         <v>-6200</v>
       </c>
       <c r="L33" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="M33" s="3">
         <v>-6600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-10100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-73300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-21300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-19900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-20600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-23200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-24700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-167400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-40200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-21500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-23200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-15200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-12000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-12200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9400</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-6200</v>
       </c>
       <c r="K35" s="3">
         <v>-6200</v>
       </c>
       <c r="L35" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="M35" s="3">
         <v>-6600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-10100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-73300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-21300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-19900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-20600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-23200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-24700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-167400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-40200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-21500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-23200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-15200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,127 +3351,131 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E41" s="3">
         <v>19300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>22000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>28200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>19900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>29600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>19100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>30600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>15400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>20600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>30200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>30900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>35500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>42800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>50500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>42300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>52300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>103400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>118500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>57600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>73000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>96500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>57600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>43800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>34200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>65100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>62000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>49500</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E42" s="3">
         <v>13400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>17600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>22100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>41600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>53900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>48500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>66900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>62600</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3430,22 +3519,25 @@
         <v>0</v>
       </c>
       <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="3">
         <v>12100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>57100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>44400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>59600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3473,68 +3565,71 @@
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M43" s="3">
         <v>300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>10100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>10900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>10800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>15800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>11200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>10400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>8300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>100</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AD43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3571,8 +3666,8 @@
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3580,39 +3675,39 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S44" s="3">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T44" s="3">
         <v>7300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>8100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>8300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>8100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>7400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>6700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1400</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC44" s="3" t="s">
         <v>5</v>
       </c>
@@ -3622,8 +3717,11 @@
       <c r="AE44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3660,148 +3758,154 @@
       <c r="N45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P45" s="3">
         <v>2200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>6600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>29300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>19100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2100</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>3700</v>
       </c>
       <c r="AD45" s="3">
         <v>3700</v>
       </c>
       <c r="AE45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AF45" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E46" s="3">
         <v>35900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>44300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>54900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>64400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>73500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>83800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>90200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>96000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>17500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>23000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>33000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>38300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>44000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>51900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>60700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>63200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>76100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>128400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>143100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>87300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>98200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>119300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>98400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>76400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>93400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>113100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>125200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>139500</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3838,8 +3942,8 @@
       <c r="N47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3874,23 +3978,26 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB47" s="3">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC47" s="3">
         <v>2000</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3901,16 +4008,16 @@
         <v>100</v>
       </c>
       <c r="F48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G48" s="3">
         <v>200</v>
       </c>
       <c r="H48" s="3">
+        <v>200</v>
+      </c>
+      <c r="I48" s="3">
         <v>100</v>
-      </c>
-      <c r="I48" s="3">
-        <v>200</v>
       </c>
       <c r="J48" s="3">
         <v>200</v>
@@ -3918,8 +4025,8 @@
       <c r="K48" s="3">
         <v>200</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
+      <c r="L48" s="3">
+        <v>200</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>5</v>
@@ -3927,59 +4034,62 @@
       <c r="N48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="3">
         <v>100</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>300</v>
       </c>
       <c r="R48" s="3">
         <v>300</v>
       </c>
       <c r="S48" s="3">
+        <v>300</v>
+      </c>
+      <c r="T48" s="3">
         <v>400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5400</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>4600</v>
       </c>
       <c r="AA48" s="3">
         <v>4600</v>
       </c>
       <c r="AB48" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AC48" s="3">
         <v>900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4043,20 +4153,20 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>5</v>
+      <c r="X49" s="3">
+        <v>0</v>
       </c>
       <c r="Y49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="Z49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA49" s="3">
         <v>4000</v>
       </c>
-      <c r="AA49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB49" s="3" t="s">
-        <v>5</v>
+      <c r="AB49" s="3">
+        <v>0</v>
       </c>
       <c r="AC49" s="3" t="s">
         <v>5</v>
@@ -4067,8 +4177,11 @@
       <c r="AE49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,97 +4361,103 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
         <v>200</v>
       </c>
       <c r="F52" s="3">
+        <v>200</v>
+      </c>
+      <c r="G52" s="3">
         <v>1300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>53500</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>200</v>
       </c>
       <c r="AB52" s="3">
         <v>200</v>
       </c>
       <c r="AC52" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD52" s="3">
         <v>100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,97 +4545,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E54" s="3">
         <v>36100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>44700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>56400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>66900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>76200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>86600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>91700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>97700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>25000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>35300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>40800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>46900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>55200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>64300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>67000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>81300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>134000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>149200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>93700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>107700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>130800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>160500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>81200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>96600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>114400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>126300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>139900</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,97 +4707,101 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>10100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>10000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>14100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>19400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4679,7 +4812,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G58" s="3">
         <v>100</v>
@@ -4697,7 +4830,7 @@
         <v>100</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -4724,11 +4857,11 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>33400</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>5</v>
       </c>
@@ -4744,8 +4877,8 @@
       <c r="AA58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
+      <c r="AB58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC58" s="3">
         <v>0</v>
@@ -4756,186 +4889,195 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>5</v>
+      <c r="E59" s="3">
+        <v>200</v>
       </c>
       <c r="F59" s="3">
-        <v>3400</v>
+        <v>600</v>
       </c>
       <c r="G59" s="3">
         <v>3400</v>
       </c>
       <c r="H59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I59" s="3">
         <v>1300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2300</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N59" s="3">
         <v>1900</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P59" s="3">
         <v>7000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>13400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>14200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>18100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>17000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>18600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>14300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>42500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>16900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>6500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>7200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>6800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E60" s="3">
         <v>4000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7500</v>
-      </c>
-      <c r="L60" s="3">
-        <v>6400</v>
       </c>
       <c r="M60" s="3">
         <v>6400</v>
       </c>
       <c r="N60" s="3">
+        <v>6400</v>
+      </c>
+      <c r="O60" s="3">
         <v>7500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9300</v>
-      </c>
-      <c r="P60" s="3">
-        <v>6800</v>
       </c>
       <c r="Q60" s="3">
         <v>6800</v>
       </c>
       <c r="R60" s="3">
+        <v>6800</v>
+      </c>
+      <c r="S60" s="3">
         <v>8600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>18400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>21000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>57600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>21500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>21800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>23200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>24200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>56600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>29300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>9500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>11900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>10600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4958,13 +5100,13 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>100</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -4994,26 +5136,26 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>33300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>33200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>33000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>32900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>32800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>32700</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5023,8 +5165,11 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5046,8 +5191,8 @@
       <c r="I62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J62" s="3">
-        <v>1300</v>
+      <c r="J62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K62" s="3">
         <v>1300</v>
@@ -5061,8 +5206,8 @@
       <c r="N62" s="3">
         <v>1300</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>5</v>
+      <c r="O62" s="3">
+        <v>1300</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>5</v>
@@ -5073,47 +5218,50 @@
       <c r="R62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
+      <c r="S62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
         <v>1400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>300</v>
       </c>
-      <c r="AD62" s="3">
-        <v>0</v>
-      </c>
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,97 +5533,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E66" s="3">
         <v>4000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9300</v>
-      </c>
-      <c r="P66" s="3">
-        <v>6800</v>
       </c>
       <c r="Q66" s="3">
         <v>6800</v>
       </c>
       <c r="R66" s="3">
+        <v>6800</v>
+      </c>
+      <c r="S66" s="3">
         <v>8600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>18400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>22400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>59100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>56300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>56200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>58200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>59300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>91000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>63600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>9600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>12200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>10600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5718,11 +5885,11 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>200</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -5768,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,97 +6027,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-757700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-752800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-745500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-739800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-731200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-719100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-707000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-697600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-691300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-685100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-678600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-668500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-662700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-652800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-643300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-634900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-639500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-628000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-606700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-586700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-566200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-543000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-518300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-350900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-310600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-162800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-146000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-129500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-110600</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E76" s="3">
         <v>32100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>38900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>44100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>52100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>63500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>74900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>83400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>88700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>26400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>31200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>40100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>48400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>55700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>48600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>58900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>74900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>92900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>37500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>49500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>71500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>69500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>17600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>87000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>102200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>115600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>130400</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-12000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-12200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9400</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-6200</v>
       </c>
       <c r="K81" s="3">
         <v>-6200</v>
       </c>
       <c r="L81" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="M81" s="3">
         <v>-6600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-10100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-73300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-21300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-19900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-20600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-23200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-24700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-167400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-40200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-21500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-23200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-15200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,13 +6804,14 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>5</v>
+      <c r="D83" s="3">
+        <v>0</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>5</v>
@@ -6633,36 +6831,36 @@
       <c r="J83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L83" s="3">
         <v>-200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
       <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
         <v>-200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>200</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
       <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3">
         <v>100</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
       <c r="U83" s="3">
         <v>0</v>
       </c>
@@ -6670,7 +6868,7 @@
         <v>0</v>
       </c>
       <c r="W83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X83" s="3">
         <v>100</v>
@@ -6682,10 +6880,10 @@
         <v>100</v>
       </c>
       <c r="AA83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB83" s="3">
         <v>-200</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>100</v>
       </c>
       <c r="AC83" s="3">
         <v>100</v>
@@ -6694,10 +6892,13 @@
         <v>100</v>
       </c>
       <c r="AE83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-10800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-11500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-9000</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-8500</v>
       </c>
       <c r="I89" s="3">
         <v>-8500</v>
       </c>
       <c r="J89" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="K89" s="3">
         <v>-8000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-9200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-9000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-56400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-17500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-16300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-12600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-25400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-23600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-35900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-52200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-16400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-19300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-12700</v>
-      </c>
-      <c r="AD89" s="3">
-        <v>-16600</v>
       </c>
       <c r="AE89" s="3">
         <v>-16600</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3">
+        <v>-16600</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,8 +7482,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7277,12 +7497,12 @@
       <c r="F91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I91" s="3" t="s">
         <v>5</v>
       </c>
@@ -7301,8 +7521,8 @@
       <c r="N91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -7311,7 +7531,7 @@
         <v>0</v>
       </c>
       <c r="R91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S91" s="3">
         <v>-100</v>
@@ -7320,7 +7540,7 @@
         <v>-100</v>
       </c>
       <c r="U91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -7332,11 +7552,11 @@
         <v>0</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
       <c r="AA91" s="3">
         <v>0</v>
       </c>
@@ -7352,8 +7572,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,97 +7756,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E94" s="3">
         <v>4400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>4700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>19800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>12700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>19000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-62400</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>5000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>16700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>1000</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>1000</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>2000</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>21100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>66000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>5500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-7100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>15400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>27500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7690,8 +7923,8 @@
       <c r="N96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7741,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,8 +8250,11 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8020,13 +8265,13 @@
         <v>0</v>
       </c>
       <c r="F100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G100" s="3">
         <v>-100</v>
       </c>
       <c r="H100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I100" s="3">
         <v>0</v>
@@ -8035,70 +8280,73 @@
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>82700</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>39800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-33600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>73500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>8000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>53600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-23000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>23000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>3000</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8135,8 +8383,8 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -8171,11 +8419,11 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>0</v>
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC101" s="3">
         <v>0</v>
@@ -8183,96 +8431,102 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-13300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>10500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-11600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>15200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-9600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>8200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-15600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-51100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-15400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>61000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-15400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-23600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>38900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>13900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-31400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>3100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>12400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-20700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VYNE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VYNE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="92">
   <si>
     <t>VYNE</t>
   </si>
@@ -656,166 +656,170 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3">
         <v>100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>200</v>
-      </c>
-      <c r="H8" s="3">
-        <v>100</v>
       </c>
       <c r="I8" s="3">
         <v>100</v>
       </c>
       <c r="J8" s="3">
+        <v>100</v>
+      </c>
+      <c r="K8" s="3">
         <v>200</v>
-      </c>
-      <c r="K8" s="3">
-        <v>100</v>
       </c>
       <c r="L8" s="3">
         <v>100</v>
@@ -830,44 +834,44 @@
         <v>100</v>
       </c>
       <c r="P8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
         <v>200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>11700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1800</v>
       </c>
-      <c r="AB8" s="3">
-        <v>0</v>
-      </c>
       <c r="AC8" s="3">
         <v>0</v>
       </c>
@@ -875,13 +879,16 @@
         <v>0</v>
       </c>
       <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="3">
         <v>300</v>
       </c>
-      <c r="AF8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -933,33 +940,33 @@
       <c r="S9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T9" s="3">
+      <c r="T9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U9" s="3">
         <v>900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>300</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC9" s="3" t="s">
         <v>5</v>
       </c>
@@ -972,8 +979,11 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -981,25 +991,25 @@
         <v>100</v>
       </c>
       <c r="E10" s="3">
+        <v>100</v>
+      </c>
+      <c r="F10" s="3">
         <v>200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>200</v>
-      </c>
-      <c r="H10" s="3">
-        <v>100</v>
       </c>
       <c r="I10" s="3">
         <v>100</v>
       </c>
       <c r="J10" s="3">
+        <v>100</v>
+      </c>
+      <c r="K10" s="3">
         <v>200</v>
-      </c>
-      <c r="K10" s="3">
-        <v>100</v>
       </c>
       <c r="L10" s="3">
         <v>100</v>
@@ -1013,8 +1023,8 @@
       <c r="O10" s="3">
         <v>100</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
+      <c r="P10" s="3">
+        <v>100</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>5</v>
@@ -1025,33 +1035,33 @@
       <c r="S10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T10" s="3">
-        <v>0</v>
+      <c r="T10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U10" s="3">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3">
         <v>3100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>11500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1500</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1064,8 +1074,11 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,100 +1111,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>800</v>
+      </c>
+      <c r="E12" s="3">
         <v>3000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>5300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>4900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>9700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>10200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>7200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>4300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>4100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>4500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>19500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>5000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>4300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>7800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>6600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>13100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>16000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>11800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>12500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>12600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>10800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,23 +1299,26 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3">
         <v>-1300</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1323,8 +1343,8 @@
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1374,8 +1394,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E17" s="3">
         <v>5300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>39800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>21900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>26300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>26800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>178900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>41600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>21900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>23200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>19400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>16200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-7800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-7500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-9200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-12800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-13100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-10400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-10300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-9300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-8300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-8700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-38900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-17800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-9500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-9800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-22000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-23500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-167200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-39800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-21900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-23200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-19400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-15900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-18400</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,35 +1748,36 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E20" s="3">
         <v>1500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-500</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3">
         <v>3100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1000</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1756,44 +1790,44 @@
       <c r="O20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>700</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>400</v>
       </c>
       <c r="AC20" s="3">
         <v>400</v>
@@ -1802,105 +1836,111 @@
         <v>400</v>
       </c>
       <c r="AE20" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF20" s="3">
         <v>500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-7400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-7000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-9200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-15800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-12200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-9400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-7400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-6200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-10300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-5900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-9100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-8200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-8700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-38900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-17800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-9600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-9800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-21900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-23600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-166500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-39100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-21700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-22700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-18900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-15300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1940,8 +1980,8 @@
       <c r="O22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1953,22 +1993,22 @@
         <v>0</v>
       </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>5600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>3500</v>
-      </c>
-      <c r="V22" s="3">
-        <v>1100</v>
       </c>
       <c r="W22" s="3">
         <v>1100</v>
       </c>
       <c r="X22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Y22" s="3">
         <v>1200</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>1100</v>
       </c>
       <c r="Z22" s="3">
         <v>1100</v>
@@ -1976,123 +2016,129 @@
       <c r="AA22" s="3">
         <v>1100</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC22" s="3">
+      <c r="AB22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD22" s="3">
         <v>300</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
-      </c>
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-12000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-12200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-9400</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-6200</v>
       </c>
       <c r="L23" s="3">
         <v>-6200</v>
       </c>
       <c r="M23" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="N23" s="3">
         <v>-6100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-9300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-8200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-44700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-21300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-10700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-10900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-23200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-24700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-167700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-40200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-21500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-23200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-19000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-15400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>5</v>
+      <c r="D24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>5</v>
@@ -2100,11 +2146,11 @@
       <c r="G24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>5</v>
+      <c r="H24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>5</v>
@@ -2124,8 +2170,8 @@
       <c r="O24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2137,11 +2183,11 @@
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>-400</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
@@ -2155,28 +2201,31 @@
         <v>0</v>
       </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-300</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>0</v>
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD24" s="3">
         <v>0</v>
       </c>
       <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
         <v>-200</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-7400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-12000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-12200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9400</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-6200</v>
       </c>
       <c r="L26" s="3">
         <v>-6200</v>
       </c>
       <c r="M26" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="N26" s="3">
         <v>-6100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-10000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-8200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-44200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-21300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-10700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-10900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-23200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-24700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-167400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-40200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-21500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-23200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-19000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-15200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-7300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-12000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-12200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-10100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-44200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-21300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-10700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-10900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-23200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-24700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-167400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-40200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-21500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-23200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-19000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-15200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,19 +2601,22 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E29" s="3">
         <v>100</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
@@ -2576,43 +2637,43 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-500</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-2200</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>-200</v>
       </c>
       <c r="R29" s="3">
         <v>-200</v>
       </c>
       <c r="S29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="T29" s="3">
         <v>13400</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-29100</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W29" s="3">
         <v>-9200</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-9700</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z29" s="3">
         <v>0</v>
@@ -2626,8 +2687,8 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,35 +2886,38 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>500</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3">
         <v>-3100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1000</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>5</v>
       </c>
@@ -2860,44 +2930,44 @@
       <c r="O32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-700</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-400</v>
       </c>
       <c r="AC32" s="3">
         <v>-400</v>
@@ -2906,105 +2976,111 @@
         <v>-400</v>
       </c>
       <c r="AE32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-7300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-12000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-12200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9400</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-6200</v>
       </c>
       <c r="L33" s="3">
         <v>-6200</v>
       </c>
       <c r="M33" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="N33" s="3">
         <v>-6600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-10100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-73300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-21300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-19900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-20600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-23200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-24700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-167400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-40200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-21500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-23200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-19000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-15200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-7300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-12000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-12200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9400</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-6200</v>
       </c>
       <c r="L35" s="3">
         <v>-6200</v>
       </c>
       <c r="M35" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="N35" s="3">
         <v>-6600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-10100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-73300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-21300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-19900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-20600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-23200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-24700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-167400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-40200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-21500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-23200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-19000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-15200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,133 +3438,137 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E41" s="3">
         <v>24000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>19300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>22000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>28200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>19900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>29600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>19100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>30600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>15400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>20600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>30200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>30900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>35500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>42800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>50500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>42300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>52300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>103400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>118500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>57600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>73000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>96500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>57600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>43800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>34200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>65100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>62000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>49500</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>300</v>
+      </c>
+      <c r="E42" s="3">
         <v>5000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>13400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>17600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>22100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>41600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>53900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>48500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>66900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>62600</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -3522,22 +3612,25 @@
         <v>0</v>
       </c>
       <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
         <v>12100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>57100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>44400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>59600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>86700</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3568,68 +3661,71 @@
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N43" s="3">
         <v>300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>10100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>10900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>10800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>15800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>11200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>10400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>8300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>100</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AE43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3669,8 +3765,8 @@
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3678,39 +3774,39 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T44" s="3">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U44" s="3">
         <v>7300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>8100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>8300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>8100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>7400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>6700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1400</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD44" s="3" t="s">
         <v>5</v>
       </c>
@@ -3720,8 +3816,11 @@
       <c r="AF44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3761,151 +3860,157 @@
       <c r="O45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q45" s="3">
         <v>2200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>5800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>6600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>29300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>19100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2100</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>3700</v>
       </c>
       <c r="AE45" s="3">
         <v>3700</v>
       </c>
       <c r="AF45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AG45" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E46" s="3">
         <v>30000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>35900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>44300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>54900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>64400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>73500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>83800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>90200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>96000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>17500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>23000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>33000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>38300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>44000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>51900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>60700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>63200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>76100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>128400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>143100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>87300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>98200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>119300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>98400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>76400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>93400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>113100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>125200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>139500</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3945,8 +4050,8 @@
       <c r="O47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3981,23 +4086,26 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC47" s="3">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD47" s="3">
         <v>2000</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4011,16 +4119,16 @@
         <v>100</v>
       </c>
       <c r="G48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H48" s="3">
         <v>200</v>
       </c>
       <c r="I48" s="3">
+        <v>200</v>
+      </c>
+      <c r="J48" s="3">
         <v>100</v>
-      </c>
-      <c r="J48" s="3">
-        <v>200</v>
       </c>
       <c r="K48" s="3">
         <v>200</v>
@@ -4028,8 +4136,8 @@
       <c r="L48" s="3">
         <v>200</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>5</v>
+      <c r="M48" s="3">
+        <v>200</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>5</v>
@@ -4037,59 +4145,62 @@
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
+      <c r="P48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3">
         <v>100</v>
-      </c>
-      <c r="R48" s="3">
-        <v>300</v>
       </c>
       <c r="S48" s="3">
         <v>300</v>
       </c>
       <c r="T48" s="3">
+        <v>300</v>
+      </c>
+      <c r="U48" s="3">
         <v>400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5400</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>4600</v>
       </c>
       <c r="AB48" s="3">
         <v>4600</v>
       </c>
       <c r="AC48" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AD48" s="3">
         <v>900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4156,20 +4267,20 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>5</v>
+      <c r="Y49" s="3">
+        <v>0</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AA49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB49" s="3">
         <v>4000</v>
       </c>
-      <c r="AB49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC49" s="3" t="s">
-        <v>5</v>
+      <c r="AC49" s="3">
+        <v>0</v>
       </c>
       <c r="AD49" s="3" t="s">
         <v>5</v>
@@ -4180,8 +4291,11 @@
       <c r="AF49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4481,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E52" s="3">
         <v>100</v>
-      </c>
-      <c r="E52" s="3">
-        <v>200</v>
       </c>
       <c r="F52" s="3">
         <v>200</v>
       </c>
       <c r="G52" s="3">
+        <v>200</v>
+      </c>
+      <c r="H52" s="3">
         <v>1300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>53500</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>200</v>
       </c>
       <c r="AC52" s="3">
         <v>200</v>
       </c>
       <c r="AD52" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE52" s="3">
         <v>100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4671,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E54" s="3">
         <v>30200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>36100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>44700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>56400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>66900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>76200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>86600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>91700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>97700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>19300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>25000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>35300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>40800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>46900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>55200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>64300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>67000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>81300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>134000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>149200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>93700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>107700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>130800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>160500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>81200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>96600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>114400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>126300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>139900</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,100 +4838,104 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>7600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>10100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>10000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>14100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>19400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4815,7 +4949,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>100</v>
@@ -4833,7 +4967,7 @@
         <v>100</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -4860,11 +4994,11 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>33400</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>5</v>
       </c>
@@ -4880,8 +5014,8 @@
       <c r="AB58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
+      <c r="AC58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD58" s="3">
         <v>0</v>
@@ -4892,192 +5026,201 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3">
         <v>200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>600</v>
-      </c>
-      <c r="G59" s="3">
-        <v>3400</v>
       </c>
       <c r="H59" s="3">
         <v>3400</v>
       </c>
       <c r="I59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J59" s="3">
         <v>1300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2300</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O59" s="3">
         <v>1900</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q59" s="3">
         <v>7000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>14200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>18100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>17000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>18600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>14300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>42500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>16900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>6500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>7200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>6800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E60" s="3">
         <v>2400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7500</v>
-      </c>
-      <c r="M60" s="3">
-        <v>6400</v>
       </c>
       <c r="N60" s="3">
         <v>6400</v>
       </c>
       <c r="O60" s="3">
+        <v>6400</v>
+      </c>
+      <c r="P60" s="3">
         <v>7500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9300</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>6800</v>
       </c>
       <c r="R60" s="3">
         <v>6800</v>
       </c>
       <c r="S60" s="3">
+        <v>6800</v>
+      </c>
+      <c r="T60" s="3">
         <v>8600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>18400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>21000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>57600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>21500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>21800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>23200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>24200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>56600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>29300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>11900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>10600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5103,13 +5246,13 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L61" s="3">
         <v>100</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N61" s="3">
         <v>0</v>
@@ -5139,26 +5282,26 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>33300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>33200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>33000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>32900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>32800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>32700</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -5168,8 +5311,11 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5194,8 +5340,8 @@
       <c r="J62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K62" s="3">
-        <v>1300</v>
+      <c r="K62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L62" s="3">
         <v>1300</v>
@@ -5209,8 +5355,8 @@
       <c r="O62" s="3">
         <v>1300</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>5</v>
+      <c r="P62" s="3">
+        <v>1300</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>5</v>
@@ -5221,47 +5367,50 @@
       <c r="S62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
+      <c r="T62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
         <v>1400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>300</v>
       </c>
-      <c r="AE62" s="3">
-        <v>0</v>
-      </c>
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5691,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E66" s="3">
         <v>2400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>12300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9300</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>6800</v>
       </c>
       <c r="R66" s="3">
         <v>6800</v>
       </c>
       <c r="S66" s="3">
+        <v>6800</v>
+      </c>
+      <c r="T66" s="3">
         <v>8600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>18400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>22400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>59100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>56300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>56200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>58200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>59300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>91000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>63600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>9600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>12200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>10600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5888,11 +6056,11 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>200</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6201,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-761200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-757700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-752800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-745500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-739800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-731200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-719100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-707000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-697600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-691300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-685100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-678600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-668500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-662700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-652800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-643300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-634900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-639500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-628000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-606700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-586700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-566200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-543000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-518300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-350900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-310600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-162800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-146000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-129500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-110600</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6581,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E76" s="3">
         <v>27800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>32100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>38900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>44100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>52100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>63500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>74900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>83400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>88700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>26400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>31200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>40100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>48400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>55700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>48600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>58900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>74900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>92900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>37500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>49500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>71500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>69500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>17600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>87000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>102200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>115600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>130400</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-7300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-12000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-12200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9400</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-6200</v>
       </c>
       <c r="L81" s="3">
         <v>-6200</v>
       </c>
       <c r="M81" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="N81" s="3">
         <v>-6600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-10100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-73300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-21300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-19900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-20600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-23200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-24700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-167400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-40200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-21500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-23200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-19000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-15200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-17600</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,16 +7003,17 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
         <v>0</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>5</v>
+      <c r="E83" s="3">
+        <v>0</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>5</v>
@@ -6834,36 +7033,36 @@
       <c r="K83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M83" s="3">
         <v>-200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>200</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
       <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
         <v>-200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>200</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
       <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3">
         <v>100</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
       <c r="V83" s="3">
         <v>0</v>
       </c>
@@ -6871,7 +7070,7 @@
         <v>0</v>
       </c>
       <c r="X83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y83" s="3">
         <v>100</v>
@@ -6883,10 +7082,10 @@
         <v>100</v>
       </c>
       <c r="AB83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC83" s="3">
         <v>-200</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>100</v>
       </c>
       <c r="AD83" s="3">
         <v>100</v>
@@ -6895,10 +7094,13 @@
         <v>100</v>
       </c>
       <c r="AF83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7571,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-10800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-11500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-9000</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-8500</v>
       </c>
       <c r="J89" s="3">
         <v>-8500</v>
       </c>
       <c r="K89" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="L89" s="3">
         <v>-8000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-7100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-9200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-9000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-56400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-17500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-16300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-12600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-25400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-23600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-35900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-52200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-16400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-19300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-12700</v>
-      </c>
-      <c r="AE89" s="3">
-        <v>-16600</v>
       </c>
       <c r="AF89" s="3">
         <v>-16600</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>-16600</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7703,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7500,12 +7721,12 @@
       <c r="G91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>5</v>
       </c>
@@ -7524,8 +7745,8 @@
       <c r="O91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -7534,7 +7755,7 @@
         <v>0</v>
       </c>
       <c r="S91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T91" s="3">
         <v>-100</v>
@@ -7543,7 +7764,7 @@
         <v>-100</v>
       </c>
       <c r="V91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -7555,11 +7776,11 @@
         <v>0</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
       <c r="AB91" s="3">
         <v>0</v>
       </c>
@@ -7575,8 +7796,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7986,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E94" s="3">
         <v>8500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>4400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>4700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>19800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>12700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>19000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-62400</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>5000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>16700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>1000</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>1000</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>2000</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>21100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>66000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>5500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-7100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>15400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>27500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7926,8 +8160,8 @@
       <c r="O96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,8 +8496,11 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8268,13 +8514,13 @@
         <v>0</v>
       </c>
       <c r="G100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H100" s="3">
         <v>-100</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J100" s="3">
         <v>0</v>
@@ -8283,70 +8529,73 @@
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>82700</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>39800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-33600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>73500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>8000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>53600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-23000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>23000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>3000</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8386,8 +8635,8 @@
       <c r="O101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8422,11 +8671,11 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>0</v>
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD101" s="3">
         <v>0</v>
@@ -8434,99 +8683,105 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>600</v>
+      </c>
+      <c r="E102" s="3">
         <v>4700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>8300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-13300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>10500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-11600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>15200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-9600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-7200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-8300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>8200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-15600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-51100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-15400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>61000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-15400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-23600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>38900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>13900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-31400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>3100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>12400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-20700</v>
       </c>
     </row>
